--- a/healer-game/メモ/memo.xlsx
+++ b/healer-game/メモ/memo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VScode\healer-game\メモ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{801D46D2-068A-4C48-B0F4-402A15DAE0AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C656078A-F276-4FC1-9778-8D5A4DFE32B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16534" yWindow="686" windowWidth="35057" windowHeight="14880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="味方スキル" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3614" uniqueCount="1829">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3692" uniqueCount="1867">
   <si>
     <t>ID</t>
   </si>
@@ -11614,10 +11614,6 @@
   </si>
   <si>
     <t>D</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>14px</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -17687,6 +17683,455 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
+    <t>あらゆる行動ができなくなる</t>
+    <rPh sb="4" eb="6">
+      <t>コウドウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>石化の目</t>
+    <rPh sb="0" eb="2">
+      <t>セキカ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>メ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>debuff_petrification_eye</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>行動バフ</t>
+    <rPh sb="0" eb="2">
+      <t>コウドウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>この状態がある間、対象指定で何かを受けた時、その相手に(状態ID:debuff_petrification)を付与する。１度付与するとこの状態は解除される</t>
+    <rPh sb="2" eb="4">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>アイダ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ナニ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>アイテ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="55" eb="57">
+      <t>フヨ</t>
+    </rPh>
+    <rPh sb="61" eb="62">
+      <t>ド</t>
+    </rPh>
+    <rPh sb="62" eb="64">
+      <t>フヨ</t>
+    </rPh>
+    <rPh sb="69" eb="71">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="72" eb="74">
+      <t>カイジョ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>一度だけ目をあわせてきた対象に"石化"を付与する</t>
+    <rPh sb="0" eb="2">
+      <t>イチド</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>セキカ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>フヨ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>一度だけ対象指定を行ってきた相手に対して"石化"を付与する</t>
+    <rPh sb="0" eb="2">
+      <t>イチド</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>アイテ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>セキカ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>フヨ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>(状態Id:debuff_petrification_eye)5s</t>
+    <rPh sb="1" eb="3">
+      <t>ジョウタイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>poison_fang</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>毒牙</t>
+    <rPh sb="0" eb="2">
+      <t>ドクガ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>攻撃力 * 0.1</t>
+    <rPh sb="0" eb="3">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>80px</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>(状態ID:
+debuff_poison)</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>魔力吸収</t>
+    <rPh sb="0" eb="2">
+      <t>マリョク</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>キュウシュウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>magic_eat</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ドットダメージと魔法ダメージを除く、ダメージを受けた際に行動CDに関係なく自動で発動される、効果時間中毎秒回復する、このスキルは自動発動でのみ発動できる</t>
+    <rPh sb="8" eb="10">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ノゾ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>カンケイ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>ジドウ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>ハツドウ</t>
+    </rPh>
+    <rPh sb="46" eb="50">
+      <t>コウカジカン</t>
+    </rPh>
+    <rPh sb="50" eb="51">
+      <t>チュウ</t>
+    </rPh>
+    <rPh sb="51" eb="53">
+      <t>マイビョウ</t>
+    </rPh>
+    <rPh sb="53" eb="55">
+      <t>カイフク</t>
+    </rPh>
+    <rPh sb="64" eb="68">
+      <t>ジドウハツドウ</t>
+    </rPh>
+    <rPh sb="71" eb="73">
+      <t>ハツドウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>魔力放出</t>
+    <rPh sb="0" eb="2">
+      <t>マリョク</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ホウシュツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>受けたダメージ分 * 2</t>
+    <rPh sb="0" eb="1">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ブン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>魔法ダメージを受けた際に行動CDに関係なく自動で発動される。受けるはずだった魔法ダメージを95%軽減し、MPを回復する</t>
+    <rPh sb="0" eb="2">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>カンケイ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ジドウ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ハツドウ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>ケイゲン</t>
+    </rPh>
+    <rPh sb="55" eb="57">
+      <t>カイフク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>magic_vomit</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>(消費したmp * 0.01) * 魔力</t>
+    <rPh sb="1" eb="3">
+      <t>ショウヒ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>マリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>360px</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>魔法</t>
+    <rPh sb="0" eb="2">
+      <t>マホウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>全mp(1以上)</t>
+    <rPh sb="0" eb="1">
+      <t>ゼン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>イジョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>溶液</t>
+    <rPh sb="0" eb="2">
+      <t>ヨウエキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>solution</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>４秒</t>
+    <rPh sb="1" eb="2">
+      <t>ビョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>230px</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>スコーピックス</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ヴィバット</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ストカゲ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ヘデュモル</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>クライム</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>scopics</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>vibat</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>スピート</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>speat</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>stokage</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>hedumol</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>clime</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>近距離</t>
+  </si>
+  <si>
+    <t>近距離</t>
+    <rPh sb="0" eb="3">
+      <t>キンキョリ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>60px</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>50px</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>80px</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>100px</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>12px</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>70px</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>90px</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>11px</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>55px</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>13px</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>戦闘不可</t>
+    <rPh sb="0" eb="2">
+      <t>セントウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>フカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>y</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>n</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
     <t>行動不可になり、スキルCDや行動CDが進まなくなり、ターゲットの対象から外れる。時間の指定がない場合、解除されるまで続く</t>
     <rPh sb="0" eb="2">
       <t>コウドウ</t>
@@ -17724,149 +18169,11 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>あらゆる行動ができなくなる</t>
-    <rPh sb="4" eb="6">
-      <t>コウドウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>石化の目</t>
-    <rPh sb="0" eb="2">
-      <t>セキカ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>メ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>debuff_petrification_eye</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>行動バフ</t>
-    <rPh sb="0" eb="2">
-      <t>コウドウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>この状態がある間、対象指定で何かを受けた時、その相手に(状態ID:debuff_petrification)を付与する。１度付与するとこの状態は解除される</t>
-    <rPh sb="2" eb="4">
-      <t>ジョウタイ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>アイダ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>タイショウ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>シテイ</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>ナニ</t>
-    </rPh>
-    <rPh sb="17" eb="18">
-      <t>ウ</t>
-    </rPh>
-    <rPh sb="20" eb="21">
-      <t>トキ</t>
-    </rPh>
-    <rPh sb="24" eb="26">
-      <t>アイテ</t>
-    </rPh>
-    <rPh sb="28" eb="30">
-      <t>ジョウタイ</t>
-    </rPh>
-    <rPh sb="55" eb="57">
-      <t>フヨ</t>
-    </rPh>
-    <rPh sb="61" eb="62">
-      <t>ド</t>
-    </rPh>
-    <rPh sb="62" eb="64">
-      <t>フヨ</t>
-    </rPh>
-    <rPh sb="69" eb="71">
-      <t>ジョウタイ</t>
-    </rPh>
-    <rPh sb="72" eb="74">
-      <t>カイジョ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>一度だけ目をあわせてきた対象に"石化"を付与する</t>
-    <rPh sb="0" eb="2">
-      <t>イチド</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>メ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>タイショウ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>セキカ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>フヨ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>一度だけ対象指定を行ってきた相手に対して"石化"を付与する</t>
-    <rPh sb="0" eb="2">
-      <t>イチド</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>タイショウ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>シテイ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>オコナ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>アイテ</t>
-    </rPh>
-    <rPh sb="17" eb="18">
-      <t>タイ</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>セキカ</t>
-    </rPh>
-    <rPh sb="25" eb="27">
-      <t>フヨ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>(状態Id:debuff_petrification_eye)5s</t>
-    <rPh sb="1" eb="3">
-      <t>ジョウタイ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>poison_fang</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>毒牙</t>
-    <rPh sb="0" eb="2">
-      <t>ドクガ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>攻撃力 * 0.1</t>
-    <rPh sb="0" eb="3">
-      <t>コウゲキリョク</t>
-    </rPh>
+    <t>-</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>40px</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -17874,182 +18181,62 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>(状態ID:
-debuff_poison)</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>魔力吸収</t>
-    <rPh sb="0" eb="2">
-      <t>マリョク</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>キュウシュウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>magic_eat</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>ドットダメージと魔法ダメージを除く、ダメージを受けた際に行動CDに関係なく自動で発動される、効果時間中毎秒回復する、このスキルは自動発動でのみ発動できる</t>
-    <rPh sb="8" eb="10">
-      <t>マホウ</t>
-    </rPh>
-    <rPh sb="15" eb="16">
-      <t>ノゾ</t>
+    <t>このモンスターには、mpの上限がなく、戦闘開始時、mpが0から始まる</t>
+    <rPh sb="13" eb="15">
+      <t>ジョウゲン</t>
+    </rPh>
+    <rPh sb="19" eb="23">
+      <t>セントウカイシ</t>
     </rPh>
     <rPh sb="23" eb="24">
-      <t>ウ</t>
-    </rPh>
-    <rPh sb="26" eb="27">
-      <t>サイ</t>
-    </rPh>
-    <rPh sb="28" eb="30">
-      <t>コウドウ</t>
-    </rPh>
-    <rPh sb="33" eb="35">
-      <t>カンケイ</t>
-    </rPh>
-    <rPh sb="37" eb="39">
-      <t>ジドウ</t>
-    </rPh>
-    <rPh sb="40" eb="42">
-      <t>ハツドウ</t>
-    </rPh>
-    <rPh sb="46" eb="50">
-      <t>コウカジカン</t>
-    </rPh>
-    <rPh sb="50" eb="51">
-      <t>チュウ</t>
-    </rPh>
-    <rPh sb="51" eb="53">
-      <t>マイビョウ</t>
-    </rPh>
-    <rPh sb="53" eb="55">
-      <t>カイフク</t>
-    </rPh>
-    <rPh sb="64" eb="68">
-      <t>ジドウハツドウ</t>
-    </rPh>
-    <rPh sb="71" eb="73">
-      <t>ハツドウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>魔力放出</t>
-    <rPh sb="0" eb="2">
-      <t>マリョク</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ホウシュツ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>受けたダメージ分 * 2</t>
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>ハジ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>敵スキルID(d_enemy_attack,poisonous_stinger,clamp)</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>敵スキルID(d_enemy_attack,ultrasound,fly_double_attack,hp_bite)</t>
     <rPh sb="0" eb="1">
-      <t>ウ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>ブン</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>魔法ダメージを受けた際に行動CDに関係なく自動で発動される。受けるはずだった魔法ダメージを95%軽減し、MPを回復する</t>
-    <rPh sb="0" eb="2">
-      <t>マホウ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>ウ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>サイ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>コウドウ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>カンケイ</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>ジドウ</t>
-    </rPh>
-    <rPh sb="24" eb="26">
-      <t>ハツドウ</t>
-    </rPh>
-    <rPh sb="30" eb="31">
-      <t>ウ</t>
-    </rPh>
-    <rPh sb="38" eb="40">
-      <t>マホウ</t>
-    </rPh>
-    <rPh sb="48" eb="50">
-      <t>ケイゲン</t>
-    </rPh>
-    <rPh sb="55" eb="57">
-      <t>カイフク</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>magic_vomit</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>(消費したmp * 0.01) * 魔力</t>
-    <rPh sb="1" eb="3">
-      <t>ショウヒ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>マリョク</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>360px</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>魔法</t>
-    <rPh sb="0" eb="2">
-      <t>マホウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>全mp(1以上)</t>
+      <t>テキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>敵スキルID(d_enemy_attack,hp_bite,spider_thread)</t>
     <rPh sb="0" eb="1">
-      <t>ゼン</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>イジョウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>溶液</t>
-    <rPh sb="0" eb="2">
-      <t>ヨウエキ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>solution</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>４秒</t>
-    <rPh sb="1" eb="2">
-      <t>ビョウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>230px</t>
+      <t>テキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>敵スキルID(d_enemy_attack,jamp_attack,hardening,tail_cutting)</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>敵スキルID(d_enemy_attack,glare_at,poison_fang)</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>敵スキルID(d_enemy_attack,magic_eat,magic_vomit,solution)</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>15px</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -18241,7 +18428,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -18346,17 +18533,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -18825,7 +19002,7 @@
         <v>15</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>19</v>
@@ -19143,7 +19320,7 @@
         <v>20</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>20</v>
@@ -19381,7 +19558,7 @@
         <v>20</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="L9" s="3" t="s">
         <v>212</v>
@@ -19488,7 +19665,7 @@
         <v>20</v>
       </c>
       <c r="T10" s="3" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="U10" s="2" t="s">
         <v>51</v>
@@ -19619,7 +19796,7 @@
         <v>20</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>19</v>
@@ -20517,7 +20694,7 @@
         <v>842</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="M24" s="13" t="s">
         <v>819</v>
@@ -20579,7 +20756,7 @@
         <v>885</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="L25" s="16" t="s">
         <v>822</v>
@@ -20644,7 +20821,7 @@
         <v>843</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="M26" s="12" t="s">
         <v>819</v>
@@ -20706,7 +20883,7 @@
         <v>844</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="M27" s="12" t="s">
         <v>819</v>
@@ -20762,7 +20939,7 @@
         <v>813</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="G28">
         <v>10</v>
@@ -20774,7 +20951,7 @@
         <v>25</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="L28" s="4" t="s">
         <v>818</v>
@@ -20804,7 +20981,7 @@
         <v>850</v>
       </c>
       <c r="V28" s="12" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="W28" s="12" t="s">
         <v>858</v>
@@ -20845,7 +21022,7 @@
         <v>20</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="L29" s="4" t="s">
         <v>818</v>
@@ -20913,7 +21090,7 @@
         <v>20</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="L30" s="34" t="s">
         <v>817</v>
@@ -20978,7 +21155,7 @@
         <v>1025</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>321</v>
@@ -21044,7 +21221,7 @@
         <v>1026</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="L32" s="16" t="s">
         <v>678</v>
@@ -21112,7 +21289,7 @@
         <v>1027</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="M33" s="12" t="s">
         <v>321</v>
@@ -21177,7 +21354,7 @@
         <v>1028</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="M34" s="12" t="s">
         <v>321</v>
@@ -21236,7 +21413,7 @@
         <v>813</v>
       </c>
       <c r="F35" s="12" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="G35">
         <v>10</v>
@@ -21248,7 +21425,7 @@
         <v>25</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="L35" s="4" t="s">
         <v>244</v>
@@ -21281,7 +21458,7 @@
         <v>850</v>
       </c>
       <c r="V35" s="12" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="W35" s="12" t="s">
         <v>1043</v>
@@ -21322,7 +21499,7 @@
         <v>20</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="L36" s="4" t="s">
         <v>244</v>
@@ -21464,7 +21641,7 @@
         <v>1025</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="M38" s="13" t="s">
         <v>321</v>
@@ -21530,7 +21707,7 @@
         <v>1026</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="L39" s="16" t="s">
         <v>678</v>
@@ -21599,7 +21776,7 @@
         <v>1027</v>
       </c>
       <c r="K40" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="M40" s="12" t="s">
         <v>321</v>
@@ -21665,7 +21842,7 @@
         <v>1028</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="M41" s="12" t="s">
         <v>321</v>
@@ -21796,7 +21973,7 @@
         <v>1194</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="F43" s="12" t="s">
         <v>1196</v>
@@ -21835,7 +22012,7 @@
         <v>1197</v>
       </c>
       <c r="T43" s="12" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="U43" s="12" t="s">
         <v>1204</v>
@@ -21858,124 +22035,124 @@
     </row>
     <row r="44" spans="1:26" ht="36">
       <c r="A44" s="4" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>389</v>
       </c>
       <c r="C44" s="12" t="s">
+        <v>1344</v>
+      </c>
+      <c r="D44" s="5" t="s">
         <v>1345</v>
       </c>
-      <c r="D44" s="5" t="s">
+      <c r="E44" s="12" t="s">
         <v>1346</v>
       </c>
-      <c r="E44" s="12" t="s">
+      <c r="P44" s="12" t="s">
         <v>1347</v>
       </c>
-      <c r="P44" s="12" t="s">
-        <v>1348</v>
-      </c>
       <c r="S44" s="12" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="U44" s="12"/>
       <c r="V44" s="12" t="s">
+        <v>1349</v>
+      </c>
+      <c r="W44" s="12" t="s">
         <v>1350</v>
-      </c>
-      <c r="W44" s="12" t="s">
-        <v>1351</v>
       </c>
     </row>
     <row r="45" spans="1:26" ht="36">
       <c r="A45" s="34" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="B45" s="4" t="s">
+        <v>1351</v>
+      </c>
+      <c r="C45" s="12" t="s">
+        <v>1344</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>1345</v>
+      </c>
+      <c r="E45" s="12" t="s">
         <v>1352</v>
       </c>
-      <c r="C45" s="12" t="s">
-        <v>1345</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>1346</v>
-      </c>
-      <c r="E45" s="12" t="s">
+      <c r="P45" s="12" t="s">
         <v>1353</v>
       </c>
-      <c r="P45" s="12" t="s">
+      <c r="S45" s="4" t="s">
+        <v>1355</v>
+      </c>
+      <c r="U45" s="12" t="s">
         <v>1354</v>
       </c>
-      <c r="S45" s="4" t="s">
+      <c r="V45" s="12" t="s">
         <v>1356</v>
       </c>
-      <c r="U45" s="12" t="s">
-        <v>1355</v>
-      </c>
-      <c r="V45" s="12" t="s">
+      <c r="W45" s="12" t="s">
         <v>1357</v>
-      </c>
-      <c r="W45" s="12" t="s">
-        <v>1358</v>
       </c>
     </row>
     <row r="46" spans="1:26" ht="54">
       <c r="A46" s="34" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>391</v>
       </c>
       <c r="C46" s="12" t="s">
+        <v>1344</v>
+      </c>
+      <c r="D46" s="5" t="s">
         <v>1345</v>
       </c>
-      <c r="D46" s="5" t="s">
-        <v>1346</v>
-      </c>
       <c r="E46" s="12" t="s">
+        <v>1358</v>
+      </c>
+      <c r="P46" s="12" t="s">
+        <v>1347</v>
+      </c>
+      <c r="S46" s="34" t="s">
         <v>1359</v>
-      </c>
-      <c r="P46" s="12" t="s">
-        <v>1348</v>
-      </c>
-      <c r="S46" s="34" t="s">
-        <v>1360</v>
       </c>
       <c r="U46" s="12"/>
       <c r="V46" s="12" t="s">
+        <v>1360</v>
+      </c>
+      <c r="W46" s="11" t="s">
         <v>1361</v>
-      </c>
-      <c r="W46" s="11" t="s">
-        <v>1362</v>
       </c>
     </row>
     <row r="47" spans="1:26" ht="54">
       <c r="A47" s="34" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>388</v>
       </c>
       <c r="C47" s="12" t="s">
+        <v>1344</v>
+      </c>
+      <c r="D47" s="5" t="s">
         <v>1345</v>
       </c>
-      <c r="D47" s="5" t="s">
-        <v>1346</v>
-      </c>
       <c r="E47" s="12" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="P47" s="12" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="S47" s="11" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="U47" s="11"/>
       <c r="V47" s="12" t="s">
+        <v>1365</v>
+      </c>
+      <c r="W47" s="16" t="s">
         <v>1366</v>
-      </c>
-      <c r="W47" s="16" t="s">
-        <v>1367</v>
       </c>
     </row>
     <row r="48" spans="1:26" ht="72">
@@ -22028,7 +22205,7 @@
     </row>
     <row r="49" spans="1:26" ht="36">
       <c r="A49" s="12" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="C49" s="12" t="s">
         <v>161</v>
@@ -22049,7 +22226,7 @@
         <v>1025</v>
       </c>
       <c r="K49" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="M49" s="13" t="s">
         <v>321</v>
@@ -22074,27 +22251,27 @@
         <v>809</v>
       </c>
       <c r="U49" s="12" t="s">
+        <v>1444</v>
+      </c>
+      <c r="V49" s="12" t="s">
+        <v>1434</v>
+      </c>
+      <c r="W49" s="12" t="s">
         <v>1445</v>
       </c>
-      <c r="V49" s="12" t="s">
-        <v>1435</v>
-      </c>
-      <c r="W49" s="12" t="s">
-        <v>1446</v>
-      </c>
       <c r="X49" s="12" t="s">
+        <v>1450</v>
+      </c>
+      <c r="Y49" s="12" t="s">
         <v>1451</v>
       </c>
-      <c r="Y49" s="12" t="s">
-        <v>1452</v>
-      </c>
       <c r="Z49" s="12" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="50" spans="1:26" ht="54">
       <c r="A50" s="12" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="C50" s="12" t="s">
         <v>161</v>
@@ -22115,7 +22292,7 @@
         <v>1026</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="L50" s="16" t="s">
         <v>678</v>
@@ -22143,27 +22320,27 @@
         <v>810</v>
       </c>
       <c r="U50" s="12" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="V50" s="12" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="W50" s="12" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="X50" s="12" t="s">
+        <v>1450</v>
+      </c>
+      <c r="Y50" s="12" t="s">
         <v>1451</v>
       </c>
-      <c r="Y50" s="12" t="s">
-        <v>1452</v>
-      </c>
       <c r="Z50" s="12" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="51" spans="1:26" ht="36">
       <c r="A51" s="12" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="C51" s="12" t="s">
         <v>161</v>
@@ -22184,7 +22361,7 @@
         <v>1027</v>
       </c>
       <c r="K51" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="M51" s="12" t="s">
         <v>321</v>
@@ -22209,27 +22386,27 @@
         <v>811</v>
       </c>
       <c r="U51" s="12" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="V51" s="12" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="W51" s="12" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="X51" s="12" t="s">
+        <v>1450</v>
+      </c>
+      <c r="Y51" s="12" t="s">
         <v>1451</v>
       </c>
-      <c r="Y51" s="12" t="s">
-        <v>1452</v>
-      </c>
       <c r="Z51" s="12" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="52" spans="1:26" ht="54">
       <c r="A52" s="12" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="C52" s="12" t="s">
         <v>161</v>
@@ -22250,7 +22427,7 @@
         <v>1028</v>
       </c>
       <c r="K52" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="M52" s="12" t="s">
         <v>321</v>
@@ -22275,27 +22452,27 @@
         <v>812</v>
       </c>
       <c r="U52" s="12" t="s">
+        <v>1448</v>
+      </c>
+      <c r="V52" s="12" t="s">
+        <v>1437</v>
+      </c>
+      <c r="W52" s="12" t="s">
         <v>1449</v>
       </c>
-      <c r="V52" s="12" t="s">
-        <v>1438</v>
-      </c>
-      <c r="W52" s="12" t="s">
+      <c r="X52" s="12" t="s">
         <v>1450</v>
       </c>
-      <c r="X52" s="12" t="s">
+      <c r="Y52" s="12" t="s">
         <v>1451</v>
       </c>
-      <c r="Y52" s="12" t="s">
-        <v>1452</v>
-      </c>
       <c r="Z52" s="12" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="53" spans="1:26" ht="90">
       <c r="A53" s="12" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="C53" s="12" t="s">
         <v>161</v>
@@ -22307,7 +22484,7 @@
         <v>813</v>
       </c>
       <c r="F53" s="12" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="G53">
         <v>10</v>
@@ -22319,7 +22496,7 @@
         <v>25</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="L53" s="4" t="s">
         <v>244</v>
@@ -22347,27 +22524,27 @@
         <v>813</v>
       </c>
       <c r="U53" s="12" t="s">
+        <v>1453</v>
+      </c>
+      <c r="V53" s="12" t="s">
+        <v>1439</v>
+      </c>
+      <c r="W53" s="12" t="s">
         <v>1454</v>
       </c>
-      <c r="V53" s="12" t="s">
-        <v>1440</v>
-      </c>
-      <c r="W53" s="12" t="s">
+      <c r="X53" s="12" t="s">
+        <v>1452</v>
+      </c>
+      <c r="Y53" s="12" t="s">
         <v>1455</v>
       </c>
-      <c r="X53" s="12" t="s">
-        <v>1453</v>
-      </c>
-      <c r="Y53" s="12" t="s">
-        <v>1456</v>
-      </c>
       <c r="Z53" s="12" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="54" spans="1:26" ht="54">
       <c r="A54" s="12" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="C54" s="12" t="s">
         <v>161</v>
@@ -22391,7 +22568,7 @@
         <v>20</v>
       </c>
       <c r="K54" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="L54" s="4" t="s">
         <v>244</v>
@@ -22419,27 +22596,27 @@
         <v>309</v>
       </c>
       <c r="U54" s="12" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="V54" s="12" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="W54" s="12" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="X54" s="12" t="s">
+        <v>1457</v>
+      </c>
+      <c r="Y54" s="12" t="s">
         <v>1458</v>
       </c>
-      <c r="Y54" s="12" t="s">
+      <c r="Z54" s="12" t="s">
         <v>1459</v>
-      </c>
-      <c r="Z54" s="12" t="s">
-        <v>1460</v>
       </c>
     </row>
     <row r="55" spans="1:26" ht="36">
       <c r="A55" s="12" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="C55" s="12" t="s">
         <v>161</v>
@@ -22448,7 +22625,7 @@
         <v>164</v>
       </c>
       <c r="E55" s="12" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="F55" s="12" t="s">
         <v>1031</v>
@@ -22475,7 +22652,7 @@
         <v>830</v>
       </c>
       <c r="O55" s="12" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="P55" s="12" t="s">
         <v>1048</v>
@@ -22487,31 +22664,31 @@
         <v>212</v>
       </c>
       <c r="S55" s="12" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="T55" s="12" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="U55" s="12"/>
       <c r="V55" s="12" t="s">
+        <v>1430</v>
+      </c>
+      <c r="W55" s="12" t="s">
         <v>1431</v>
       </c>
-      <c r="W55" s="12" t="s">
+      <c r="X55" s="12" t="s">
         <v>1432</v>
-      </c>
-      <c r="X55" s="12" t="s">
-        <v>1433</v>
       </c>
       <c r="Y55" s="12" t="s">
         <v>1059</v>
       </c>
       <c r="Z55" s="12" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="56" spans="1:26" ht="54">
       <c r="A56" s="12" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>162</v>
@@ -22523,7 +22700,7 @@
         <v>164</v>
       </c>
       <c r="E56" s="12" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="F56" s="12" t="s">
         <v>587</v>
@@ -22565,31 +22742,31 @@
         <v>241</v>
       </c>
       <c r="S56" s="12" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="T56" s="12" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="U56" s="12"/>
       <c r="V56" s="16" t="s">
+        <v>1517</v>
+      </c>
+      <c r="W56" s="12" t="s">
         <v>1518</v>
       </c>
-      <c r="W56" s="12" t="s">
+      <c r="X56" s="12" t="s">
         <v>1519</v>
       </c>
-      <c r="X56" s="12" t="s">
+      <c r="Y56" s="12" t="s">
         <v>1520</v>
       </c>
-      <c r="Y56" s="12" t="s">
+      <c r="Z56" s="12" t="s">
         <v>1521</v>
-      </c>
-      <c r="Z56" s="12" t="s">
-        <v>1522</v>
       </c>
     </row>
     <row r="57" spans="1:26" ht="54">
       <c r="A57" s="12" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="B57" s="4" t="s">
         <v>162</v>
@@ -22601,7 +22778,7 @@
         <v>164</v>
       </c>
       <c r="E57" s="12" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="F57" s="12" t="s">
         <v>587</v>
@@ -22643,31 +22820,31 @@
         <v>241</v>
       </c>
       <c r="S57" s="12" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="T57" s="12" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="U57" s="12"/>
       <c r="V57" s="16" t="s">
+        <v>1530</v>
+      </c>
+      <c r="W57" s="12" t="s">
         <v>1531</v>
       </c>
-      <c r="W57" s="12" t="s">
+      <c r="X57" s="12" t="s">
         <v>1532</v>
       </c>
-      <c r="X57" s="12" t="s">
+      <c r="Y57" s="12" t="s">
         <v>1533</v>
       </c>
-      <c r="Y57" s="12" t="s">
+      <c r="Z57" s="12" t="s">
         <v>1534</v>
-      </c>
-      <c r="Z57" s="12" t="s">
-        <v>1535</v>
       </c>
     </row>
     <row r="58" spans="1:26" ht="54">
       <c r="A58" s="12" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="B58" s="4" t="s">
         <v>162</v>
@@ -22679,7 +22856,7 @@
         <v>164</v>
       </c>
       <c r="E58" s="12" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="F58" s="12" t="s">
         <v>587</v>
@@ -22721,592 +22898,592 @@
         <v>241</v>
       </c>
       <c r="S58" s="12" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="T58" s="12" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="U58" s="12"/>
       <c r="V58" s="16" t="s">
+        <v>1542</v>
+      </c>
+      <c r="W58" s="12" t="s">
         <v>1543</v>
       </c>
-      <c r="W58" s="12" t="s">
+      <c r="X58" s="12" t="s">
         <v>1544</v>
       </c>
-      <c r="X58" s="12" t="s">
+      <c r="Y58" s="12" t="s">
         <v>1545</v>
       </c>
-      <c r="Y58" s="12" t="s">
+      <c r="Z58" s="12" t="s">
         <v>1546</v>
-      </c>
-      <c r="Z58" s="12" t="s">
-        <v>1547</v>
       </c>
     </row>
     <row r="59" spans="1:26" ht="36">
       <c r="A59" s="12" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="B59" s="4" t="s">
+        <v>1551</v>
+      </c>
+      <c r="C59" s="13" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D59" s="5" t="s">
         <v>1552</v>
       </c>
-      <c r="C59" s="13" t="s">
-        <v>1551</v>
-      </c>
-      <c r="D59" s="5" t="s">
+      <c r="E59" s="12" t="s">
+        <v>1562</v>
+      </c>
+      <c r="F59" s="12" t="s">
         <v>1553</v>
-      </c>
-      <c r="E59" s="12" t="s">
-        <v>1563</v>
-      </c>
-      <c r="F59" s="12" t="s">
-        <v>1554</v>
       </c>
       <c r="G59">
         <v>5</v>
       </c>
       <c r="H59" s="16" t="s">
+        <v>1554</v>
+      </c>
+      <c r="J59" s="34" t="s">
         <v>1555</v>
       </c>
-      <c r="J59" s="34" t="s">
+      <c r="K59" s="12" t="s">
         <v>1556</v>
       </c>
-      <c r="K59" s="12" t="s">
+      <c r="L59" s="12" t="s">
         <v>1557</v>
       </c>
-      <c r="L59" s="12" t="s">
+      <c r="M59" s="13" t="s">
         <v>1558</v>
       </c>
-      <c r="M59" s="13" t="s">
+      <c r="N59" s="12" t="s">
         <v>1559</v>
       </c>
-      <c r="N59" s="12" t="s">
+      <c r="O59" s="13" t="s">
+        <v>1555</v>
+      </c>
+      <c r="P59" s="13" t="s">
         <v>1560</v>
       </c>
-      <c r="O59" s="13" t="s">
-        <v>1556</v>
-      </c>
-      <c r="P59" s="13" t="s">
+      <c r="Q59" s="12" t="s">
+        <v>1555</v>
+      </c>
+      <c r="R59" s="13" t="s">
         <v>1561</v>
       </c>
-      <c r="Q59" s="12" t="s">
-        <v>1556</v>
-      </c>
-      <c r="R59" s="13" t="s">
+      <c r="S59" s="12" t="s">
+        <v>1555</v>
+      </c>
+      <c r="T59" s="12" t="s">
         <v>1562</v>
       </c>
-      <c r="S59" s="12" t="s">
-        <v>1556</v>
-      </c>
-      <c r="T59" s="12" t="s">
-        <v>1563</v>
-      </c>
       <c r="U59" s="12" t="s">
+        <v>1564</v>
+      </c>
+      <c r="V59" s="16" t="s">
         <v>1565</v>
       </c>
-      <c r="V59" s="16" t="s">
+      <c r="W59" s="12" t="s">
+        <v>1569</v>
+      </c>
+      <c r="X59" s="12" t="s">
         <v>1566</v>
       </c>
-      <c r="W59" s="12" t="s">
-        <v>1570</v>
-      </c>
-      <c r="X59" s="12" t="s">
+      <c r="Y59" s="12" t="s">
         <v>1567</v>
       </c>
-      <c r="Y59" s="12" t="s">
+      <c r="Z59" s="12" t="s">
         <v>1568</v>
-      </c>
-      <c r="Z59" s="12" t="s">
-        <v>1569</v>
       </c>
     </row>
     <row r="60" spans="1:26" ht="37.799999999999997" customHeight="1">
       <c r="A60" s="12" t="s">
+        <v>1574</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>1573</v>
+      </c>
+      <c r="C60" s="13" t="s">
+        <v>1572</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>1571</v>
+      </c>
+      <c r="E60" s="12" t="s">
+        <v>1570</v>
+      </c>
+      <c r="F60" s="12" t="s">
         <v>1575</v>
       </c>
-      <c r="B60" s="4" t="s">
-        <v>1574</v>
-      </c>
-      <c r="C60" s="13" t="s">
-        <v>1573</v>
-      </c>
-      <c r="D60" s="5" t="s">
-        <v>1572</v>
-      </c>
-      <c r="E60" s="12" t="s">
-        <v>1571</v>
-      </c>
-      <c r="F60" s="12" t="s">
+      <c r="G60" s="12" t="s">
         <v>1576</v>
       </c>
-      <c r="G60" s="12" t="s">
-        <v>1577</v>
-      </c>
       <c r="H60" s="16" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="J60">
         <v>10</v>
       </c>
       <c r="K60" s="12" t="s">
+        <v>1577</v>
+      </c>
+      <c r="L60" s="12" t="s">
+        <v>1580</v>
+      </c>
+      <c r="M60" s="13" t="s">
         <v>1578</v>
       </c>
-      <c r="L60" s="12" t="s">
-        <v>1581</v>
-      </c>
-      <c r="M60" s="13" t="s">
-        <v>1579</v>
-      </c>
       <c r="N60" s="12" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="O60" s="13" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="P60" s="13" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="S60" s="12" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="T60" s="12" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="U60" s="34"/>
       <c r="V60" s="16" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="W60" s="12" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="X60" s="12" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="Y60" s="12" t="s">
         <v>1184</v>
       </c>
       <c r="Z60" s="12" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="61" spans="1:26" ht="54.6" customHeight="1">
       <c r="A61" s="12" t="s">
+        <v>1596</v>
+      </c>
+      <c r="B61" s="11" t="s">
+        <v>1595</v>
+      </c>
+      <c r="C61" s="13" t="s">
+        <v>1594</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>1593</v>
+      </c>
+      <c r="E61" s="12" t="s">
+        <v>1592</v>
+      </c>
+      <c r="F61" s="12" t="s">
         <v>1597</v>
       </c>
-      <c r="B61" s="11" t="s">
-        <v>1596</v>
-      </c>
-      <c r="C61" s="13" t="s">
-        <v>1595</v>
-      </c>
-      <c r="D61" s="5" t="s">
-        <v>1594</v>
-      </c>
-      <c r="E61" s="12" t="s">
-        <v>1593</v>
-      </c>
-      <c r="F61" s="12" t="s">
+      <c r="G61" s="12" t="s">
         <v>1598</v>
-      </c>
-      <c r="G61" s="12" t="s">
-        <v>1599</v>
       </c>
       <c r="J61">
         <v>20</v>
       </c>
       <c r="K61" s="12" t="s">
+        <v>1599</v>
+      </c>
+      <c r="L61" s="12" t="s">
+        <v>1598</v>
+      </c>
+      <c r="M61" s="13" t="s">
         <v>1600</v>
       </c>
-      <c r="L61" s="12" t="s">
-        <v>1599</v>
-      </c>
-      <c r="M61" s="13" t="s">
-        <v>1601</v>
-      </c>
       <c r="N61" s="12" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="P61" s="13" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="S61" s="11" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="T61" s="12" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="V61" s="16" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="W61" s="12" t="s">
+        <v>1609</v>
+      </c>
+      <c r="X61" s="12" t="s">
         <v>1610</v>
       </c>
-      <c r="X61" s="12" t="s">
+      <c r="Y61" s="12" t="s">
         <v>1611</v>
       </c>
-      <c r="Y61" s="12" t="s">
+      <c r="Z61" s="12" t="s">
         <v>1612</v>
-      </c>
-      <c r="Z61" s="12" t="s">
-        <v>1613</v>
       </c>
     </row>
     <row r="62" spans="1:26" ht="51" customHeight="1">
       <c r="A62" s="12" t="s">
+        <v>1619</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>1615</v>
+      </c>
+      <c r="C62" s="13" t="s">
+        <v>1616</v>
+      </c>
+      <c r="D62" s="5" t="s">
+        <v>1618</v>
+      </c>
+      <c r="E62" s="12" t="s">
+        <v>1617</v>
+      </c>
+      <c r="F62" s="12" t="s">
         <v>1620</v>
-      </c>
-      <c r="B62" s="4" t="s">
-        <v>1616</v>
-      </c>
-      <c r="C62" s="13" t="s">
-        <v>1617</v>
-      </c>
-      <c r="D62" s="5" t="s">
-        <v>1619</v>
-      </c>
-      <c r="E62" s="12" t="s">
-        <v>1618</v>
-      </c>
-      <c r="F62" s="12" t="s">
-        <v>1621</v>
       </c>
       <c r="G62">
         <v>10</v>
       </c>
       <c r="H62" s="16" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="J62" s="34">
         <v>30</v>
       </c>
       <c r="K62" s="12" t="s">
+        <v>1623</v>
+      </c>
+      <c r="L62" s="12" t="s">
         <v>1624</v>
       </c>
-      <c r="L62" s="12" t="s">
+      <c r="M62" s="13" t="s">
         <v>1625</v>
       </c>
-      <c r="M62" s="13" t="s">
+      <c r="N62" s="12" t="s">
         <v>1626</v>
       </c>
-      <c r="N62" s="12" t="s">
+      <c r="O62" s="13" t="s">
+        <v>1622</v>
+      </c>
+      <c r="P62" s="12" t="s">
         <v>1627</v>
       </c>
-      <c r="O62" s="13" t="s">
-        <v>1623</v>
-      </c>
-      <c r="P62" s="12" t="s">
+      <c r="Q62" s="16" t="s">
+        <v>1622</v>
+      </c>
+      <c r="R62" s="41" t="s">
         <v>1628</v>
       </c>
-      <c r="Q62" s="16" t="s">
-        <v>1623</v>
-      </c>
-      <c r="R62" s="41" t="s">
+      <c r="S62" s="39" t="s">
         <v>1629</v>
       </c>
-      <c r="S62" s="39" t="s">
+      <c r="T62" s="12" t="s">
+        <v>1617</v>
+      </c>
+      <c r="V62" s="16" t="s">
         <v>1630</v>
       </c>
-      <c r="T62" s="12" t="s">
-        <v>1618</v>
-      </c>
-      <c r="V62" s="16" t="s">
-        <v>1631</v>
-      </c>
       <c r="W62" s="12" t="s">
-        <v>1646</v>
+        <v>1645</v>
       </c>
       <c r="X62" s="12" t="s">
         <v>860</v>
       </c>
       <c r="Y62" s="12" t="s">
+        <v>1631</v>
+      </c>
+      <c r="Z62" s="12" t="s">
         <v>1632</v>
-      </c>
-      <c r="Z62" s="12" t="s">
-        <v>1633</v>
       </c>
     </row>
     <row r="63" spans="1:26" ht="35.4" customHeight="1">
       <c r="A63" s="12" t="s">
+        <v>1637</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>1636</v>
+      </c>
+      <c r="C63" s="13" t="s">
+        <v>1635</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>1634</v>
+      </c>
+      <c r="E63" s="12" t="s">
+        <v>1633</v>
+      </c>
+      <c r="F63" s="12" t="s">
         <v>1638</v>
-      </c>
-      <c r="B63" s="4" t="s">
-        <v>1637</v>
-      </c>
-      <c r="C63" s="13" t="s">
-        <v>1636</v>
-      </c>
-      <c r="D63" s="5" t="s">
-        <v>1635</v>
-      </c>
-      <c r="E63" s="12" t="s">
-        <v>1634</v>
-      </c>
-      <c r="F63" s="12" t="s">
-        <v>1639</v>
       </c>
       <c r="G63">
         <v>30</v>
       </c>
       <c r="H63" s="16" t="s">
-        <v>1640</v>
+        <v>1639</v>
       </c>
       <c r="J63">
         <v>15</v>
       </c>
       <c r="K63" s="12" t="s">
+        <v>1640</v>
+      </c>
+      <c r="L63" s="12" t="s">
         <v>1641</v>
       </c>
-      <c r="L63" s="12" t="s">
+      <c r="M63" s="13" t="s">
         <v>1642</v>
       </c>
-      <c r="M63" s="13" t="s">
+      <c r="N63" s="12" t="s">
         <v>1643</v>
       </c>
-      <c r="N63" s="12" t="s">
+      <c r="O63" s="13" t="s">
+        <v>1641</v>
+      </c>
+      <c r="P63" s="12" t="s">
         <v>1644</v>
       </c>
-      <c r="O63" s="13" t="s">
-        <v>1642</v>
-      </c>
-      <c r="P63" s="12" t="s">
-        <v>1645</v>
-      </c>
       <c r="Q63" s="16" t="s">
-        <v>1642</v>
+        <v>1641</v>
       </c>
       <c r="R63" s="34" t="s">
         <v>242</v>
       </c>
       <c r="T63" s="12" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="U63" s="34" t="s">
+        <v>1649</v>
+      </c>
+      <c r="V63" s="16" t="s">
         <v>1650</v>
       </c>
-      <c r="V63" s="16" t="s">
+      <c r="W63" s="12" t="s">
         <v>1651</v>
       </c>
-      <c r="W63" s="12" t="s">
-        <v>1652</v>
-      </c>
       <c r="X63" s="12" t="s">
+        <v>1646</v>
+      </c>
+      <c r="Y63" s="12" t="s">
         <v>1647</v>
       </c>
-      <c r="Y63" s="12" t="s">
+      <c r="Z63" s="12" t="s">
         <v>1648</v>
-      </c>
-      <c r="Z63" s="12" t="s">
-        <v>1649</v>
       </c>
     </row>
     <row r="64" spans="1:26" ht="36">
       <c r="A64" s="12" t="s">
+        <v>1655</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>1654</v>
+      </c>
+      <c r="C64" s="13" t="s">
+        <v>1653</v>
+      </c>
+      <c r="D64" s="5" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E64" s="12" t="s">
+        <v>1670</v>
+      </c>
+      <c r="F64" s="12" t="s">
         <v>1656</v>
       </c>
-      <c r="B64" s="4" t="s">
-        <v>1655</v>
-      </c>
-      <c r="C64" s="13" t="s">
-        <v>1654</v>
-      </c>
-      <c r="D64" s="5" t="s">
-        <v>1653</v>
-      </c>
-      <c r="E64" s="12" t="s">
-        <v>1671</v>
-      </c>
-      <c r="F64" s="12" t="s">
+      <c r="G64" s="12" t="s">
         <v>1657</v>
-      </c>
-      <c r="G64" s="12" t="s">
-        <v>1658</v>
       </c>
       <c r="J64">
         <v>30</v>
       </c>
       <c r="K64" s="12" t="s">
+        <v>1658</v>
+      </c>
+      <c r="L64" s="12" t="s">
         <v>1659</v>
       </c>
-      <c r="L64" s="12" t="s">
+      <c r="M64" s="13" t="s">
         <v>1660</v>
       </c>
-      <c r="M64" s="13" t="s">
+      <c r="N64" s="12" t="s">
         <v>1661</v>
       </c>
-      <c r="N64" s="12" t="s">
+      <c r="O64" s="13" t="s">
+        <v>1657</v>
+      </c>
+      <c r="P64" s="12" t="s">
         <v>1662</v>
       </c>
-      <c r="O64" s="13" t="s">
-        <v>1658</v>
-      </c>
-      <c r="P64" s="12" t="s">
-        <v>1663</v>
-      </c>
       <c r="Q64" s="16" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="R64" s="34" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="S64" s="39" t="s">
+        <v>1668</v>
+      </c>
+      <c r="T64" s="12" t="s">
+        <v>1670</v>
+      </c>
+      <c r="V64" s="16" t="s">
+        <v>1697</v>
+      </c>
+      <c r="W64" s="12" t="s">
+        <v>1698</v>
+      </c>
+      <c r="X64" s="12" t="s">
         <v>1669</v>
       </c>
-      <c r="T64" s="12" t="s">
-        <v>1671</v>
-      </c>
-      <c r="V64" s="16" t="s">
-        <v>1698</v>
-      </c>
-      <c r="W64" s="12" t="s">
+      <c r="Y64" s="12" t="s">
         <v>1699</v>
       </c>
-      <c r="X64" s="12" t="s">
-        <v>1670</v>
-      </c>
-      <c r="Y64" s="12" t="s">
+      <c r="Z64" s="12" t="s">
         <v>1700</v>
-      </c>
-      <c r="Z64" s="12" t="s">
-        <v>1701</v>
       </c>
     </row>
     <row r="65" spans="1:26" ht="36">
       <c r="A65" s="12" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="B65" s="4" t="s">
+        <v>1673</v>
+      </c>
+      <c r="C65" s="13" t="s">
+        <v>1672</v>
+      </c>
+      <c r="D65" s="5" t="s">
+        <v>1671</v>
+      </c>
+      <c r="E65" s="12" t="s">
+        <v>1683</v>
+      </c>
+      <c r="F65" s="12" t="s">
         <v>1674</v>
-      </c>
-      <c r="C65" s="13" t="s">
-        <v>1673</v>
-      </c>
-      <c r="D65" s="5" t="s">
-        <v>1672</v>
-      </c>
-      <c r="E65" s="12" t="s">
-        <v>1684</v>
-      </c>
-      <c r="F65" s="12" t="s">
-        <v>1675</v>
       </c>
       <c r="G65">
         <v>20</v>
       </c>
       <c r="H65" s="16" t="s">
+        <v>1675</v>
+      </c>
+      <c r="J65" s="34" t="s">
         <v>1676</v>
       </c>
-      <c r="J65" s="34" t="s">
+      <c r="K65" s="12" t="s">
         <v>1677</v>
       </c>
-      <c r="K65" s="12" t="s">
+      <c r="L65" s="12" t="s">
         <v>1678</v>
       </c>
-      <c r="L65" s="12" t="s">
+      <c r="M65" s="13" t="s">
         <v>1679</v>
       </c>
-      <c r="M65" s="13" t="s">
+      <c r="N65" s="12" t="s">
         <v>1680</v>
       </c>
-      <c r="N65" s="12" t="s">
+      <c r="O65" s="13" t="s">
+        <v>1676</v>
+      </c>
+      <c r="P65" s="12" t="s">
         <v>1681</v>
       </c>
-      <c r="O65" s="13" t="s">
-        <v>1677</v>
-      </c>
-      <c r="P65" s="12" t="s">
+      <c r="R65" s="34" t="s">
         <v>1682</v>
       </c>
-      <c r="R65" s="34" t="s">
+      <c r="T65" s="12" t="s">
         <v>1683</v>
       </c>
-      <c r="T65" s="12" t="s">
-        <v>1684</v>
-      </c>
       <c r="V65" s="16" t="s">
+        <v>1685</v>
+      </c>
+      <c r="W65" s="12" t="s">
         <v>1686</v>
-      </c>
-      <c r="W65" s="12" t="s">
-        <v>1687</v>
       </c>
       <c r="X65" s="12" t="s">
         <v>860</v>
       </c>
       <c r="Y65" s="12" t="s">
+        <v>1631</v>
+      </c>
+      <c r="Z65" s="12" t="s">
         <v>1632</v>
-      </c>
-      <c r="Z65" s="12" t="s">
-        <v>1633</v>
       </c>
     </row>
     <row r="66" spans="1:26" ht="36">
       <c r="A66" s="12" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="C66" s="13" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="E66" s="12" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="F66" s="12" t="s">
-        <v>1675</v>
+        <v>1674</v>
       </c>
       <c r="G66">
         <v>10</v>
       </c>
       <c r="H66" s="16" t="s">
+        <v>1690</v>
+      </c>
+      <c r="J66" s="34" t="s">
+        <v>1676</v>
+      </c>
+      <c r="K66" s="12" t="s">
         <v>1691</v>
       </c>
-      <c r="J66" s="34" t="s">
-        <v>1677</v>
-      </c>
-      <c r="K66" s="12" t="s">
+      <c r="L66" s="12" t="s">
+        <v>1676</v>
+      </c>
+      <c r="M66" s="13" t="s">
+        <v>1679</v>
+      </c>
+      <c r="N66" s="12" t="s">
         <v>1692</v>
       </c>
-      <c r="L66" s="12" t="s">
-        <v>1677</v>
-      </c>
-      <c r="M66" s="13" t="s">
-        <v>1680</v>
-      </c>
-      <c r="N66" s="12" t="s">
+      <c r="O66" s="13" t="s">
+        <v>1676</v>
+      </c>
+      <c r="P66" s="12" t="s">
+        <v>1681</v>
+      </c>
+      <c r="R66" s="34" t="s">
+        <v>1682</v>
+      </c>
+      <c r="S66" s="34" t="s">
+        <v>1629</v>
+      </c>
+      <c r="T66" s="12" t="s">
+        <v>1687</v>
+      </c>
+      <c r="V66" s="16" t="s">
         <v>1693</v>
       </c>
-      <c r="O66" s="13" t="s">
-        <v>1677</v>
-      </c>
-      <c r="P66" s="12" t="s">
-        <v>1682</v>
-      </c>
-      <c r="R66" s="34" t="s">
-        <v>1683</v>
-      </c>
-      <c r="S66" s="34" t="s">
-        <v>1630</v>
-      </c>
-      <c r="T66" s="12" t="s">
-        <v>1688</v>
-      </c>
-      <c r="V66" s="16" t="s">
+      <c r="W66" s="12" t="s">
         <v>1694</v>
       </c>
-      <c r="W66" s="12" t="s">
+      <c r="X66" s="12" t="s">
+        <v>1669</v>
+      </c>
+      <c r="Y66" s="12" t="s">
         <v>1695</v>
       </c>
-      <c r="X66" s="12" t="s">
-        <v>1670</v>
-      </c>
-      <c r="Y66" s="12" t="s">
+      <c r="Z66" s="12" t="s">
         <v>1696</v>
-      </c>
-      <c r="Z66" s="12" t="s">
-        <v>1697</v>
       </c>
     </row>
     <row r="74" spans="1:26" ht="72">
@@ -23699,7 +23876,7 @@
         <v>635</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>636</v>
+        <v>614</v>
       </c>
       <c r="N5" s="3" t="s">
         <v>629</v>
@@ -24009,7 +24186,7 @@
         <v>634</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="R11" s="3" t="s">
         <v>629</v>
@@ -24070,13 +24247,13 @@
         <v>638</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="S12" s="3" t="s">
         <v>657</v>
       </c>
       <c r="T12" s="3" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="13" spans="1:25" ht="36">
@@ -24193,434 +24370,434 @@
     </row>
     <row r="15" spans="1:25">
       <c r="A15" s="12" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>1246</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="F15" s="13">
         <v>15</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="I15" s="16" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="J15" s="12" t="s">
         <v>648</v>
       </c>
       <c r="K15" s="12" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="L15" s="12" t="s">
+        <v>1254</v>
+      </c>
+      <c r="M15" s="12" t="s">
         <v>1255</v>
       </c>
-      <c r="M15" s="12" t="s">
+      <c r="N15" s="12" t="s">
+        <v>1247</v>
+      </c>
+      <c r="O15" s="12" t="s">
         <v>1256</v>
       </c>
-      <c r="N15" s="12" t="s">
-        <v>1248</v>
-      </c>
-      <c r="O15" s="12" t="s">
+      <c r="P15" s="12" t="s">
+        <v>1247</v>
+      </c>
+      <c r="Q15" s="12" t="s">
         <v>1257</v>
       </c>
-      <c r="P15" s="12" t="s">
-        <v>1248</v>
-      </c>
-      <c r="Q15" s="12" t="s">
+      <c r="R15" s="12" t="s">
+        <v>1247</v>
+      </c>
+      <c r="S15" s="12" t="s">
         <v>1258</v>
-      </c>
-      <c r="R15" s="12" t="s">
-        <v>1248</v>
-      </c>
-      <c r="S15" s="12" t="s">
-        <v>1259</v>
       </c>
     </row>
     <row r="16" spans="1:25" ht="36">
       <c r="A16" s="12" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>1246</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="F16" s="13">
         <v>5</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="I16" s="16" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="J16" s="12" t="s">
+        <v>1262</v>
+      </c>
+      <c r="K16" s="12" t="s">
+        <v>1247</v>
+      </c>
+      <c r="L16" s="12" t="s">
+        <v>1254</v>
+      </c>
+      <c r="M16" s="12" t="s">
+        <v>1261</v>
+      </c>
+      <c r="N16" s="12" t="s">
+        <v>1247</v>
+      </c>
+      <c r="O16" s="12" t="s">
+        <v>1256</v>
+      </c>
+      <c r="Q16" s="12" t="s">
+        <v>1257</v>
+      </c>
+      <c r="R16" s="12" t="s">
         <v>1263</v>
       </c>
-      <c r="K16" s="12" t="s">
-        <v>1248</v>
-      </c>
-      <c r="L16" s="12" t="s">
-        <v>1255</v>
-      </c>
-      <c r="M16" s="12" t="s">
-        <v>1262</v>
-      </c>
-      <c r="N16" s="12" t="s">
-        <v>1248</v>
-      </c>
-      <c r="O16" s="12" t="s">
-        <v>1257</v>
-      </c>
-      <c r="Q16" s="12" t="s">
-        <v>1258</v>
-      </c>
-      <c r="R16" s="12" t="s">
+      <c r="S16" s="12" t="s">
         <v>1264</v>
-      </c>
-      <c r="S16" s="12" t="s">
-        <v>1265</v>
       </c>
     </row>
     <row r="17" spans="1:23" ht="72">
       <c r="A17" s="12" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>1246</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="F17" s="13">
         <v>5</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="I17" s="16" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="J17" s="12" t="s">
+        <v>1269</v>
+      </c>
+      <c r="K17" s="12" t="s">
+        <v>1268</v>
+      </c>
+      <c r="L17" s="12" t="s">
+        <v>1254</v>
+      </c>
+      <c r="M17" s="12" t="s">
+        <v>1267</v>
+      </c>
+      <c r="O17" s="12" t="s">
+        <v>1256</v>
+      </c>
+      <c r="P17" s="12" t="s">
         <v>1270</v>
       </c>
-      <c r="K17" s="12" t="s">
-        <v>1269</v>
-      </c>
-      <c r="L17" s="12" t="s">
-        <v>1255</v>
-      </c>
-      <c r="M17" s="12" t="s">
-        <v>1268</v>
-      </c>
-      <c r="O17" s="12" t="s">
-        <v>1257</v>
-      </c>
-      <c r="P17" s="12" t="s">
-        <v>1271</v>
-      </c>
       <c r="Q17" s="12" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="S17" s="12" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="T17" s="12" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="18" spans="1:23" ht="36">
       <c r="A18" s="3" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="C18" s="14" t="s">
         <v>1246</v>
       </c>
       <c r="D18" s="3" t="s">
+        <v>1276</v>
+      </c>
+      <c r="E18" s="4" t="s">
         <v>1277</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>1278</v>
       </c>
       <c r="F18" s="2">
         <v>5</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="H18" s="2"/>
       <c r="I18" s="3" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>487</v>
       </c>
       <c r="K18" s="3" t="s">
+        <v>1247</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>1253</v>
+      </c>
+      <c r="M18" s="3" t="s">
         <v>1248</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>1254</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>1249</v>
-      </c>
       <c r="N18" s="3" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="O18" s="3" t="s">
+        <v>1256</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>1247</v>
+      </c>
+      <c r="Q18" s="3" t="s">
         <v>1257</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>1248</v>
-      </c>
-      <c r="Q18" s="3" t="s">
-        <v>1258</v>
-      </c>
       <c r="R18" s="3" t="s">
+        <v>1279</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>1276</v>
+      </c>
+      <c r="T18" s="3" t="s">
         <v>1280</v>
-      </c>
-      <c r="S18" s="3" t="s">
-        <v>1277</v>
-      </c>
-      <c r="T18" s="3" t="s">
-        <v>1281</v>
       </c>
     </row>
     <row r="19" spans="1:23" ht="72">
       <c r="A19" s="3" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="C19" s="14" t="s">
         <v>1246</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="F19" s="2">
         <v>10</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="H19" s="2"/>
       <c r="I19" s="3" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="J19" s="3" t="s">
         <v>648</v>
       </c>
       <c r="K19" s="3" t="s">
+        <v>1284</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>1253</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>1248</v>
+      </c>
+      <c r="N19" s="3" t="s">
         <v>1285</v>
       </c>
-      <c r="L19" s="3" t="s">
-        <v>1254</v>
-      </c>
-      <c r="M19" s="3" t="s">
-        <v>1249</v>
-      </c>
-      <c r="N19" s="3" t="s">
-        <v>1286</v>
-      </c>
       <c r="O19" s="3" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="P19" s="3" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="Q19" s="3" t="s">
         <v>241</v>
       </c>
       <c r="R19" s="2"/>
       <c r="S19" s="3" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="T19" s="3" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="20" spans="1:23" ht="90">
       <c r="A20" s="3" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="C20" s="14" t="s">
         <v>1246</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="F20" s="2">
         <v>10</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="H20" s="2"/>
       <c r="I20" s="3" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>672</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="N20" s="3" t="s">
+        <v>1290</v>
+      </c>
+      <c r="O20" s="3" t="s">
         <v>1291</v>
       </c>
-      <c r="O20" s="3" t="s">
+      <c r="P20" s="3" t="s">
+        <v>1247</v>
+      </c>
+      <c r="Q20" s="3" t="s">
         <v>1292</v>
-      </c>
-      <c r="P20" s="3" t="s">
-        <v>1248</v>
-      </c>
-      <c r="Q20" s="3" t="s">
-        <v>1293</v>
       </c>
       <c r="R20" s="2"/>
       <c r="S20" s="3" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="T20" s="3" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="21" spans="1:23" ht="72">
       <c r="A21" s="3" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="C21" s="14" t="s">
         <v>1246</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="F21" s="2">
         <v>10</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="H21" s="2"/>
       <c r="I21" s="3" t="s">
+        <v>1247</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>1338</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>1284</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>1253</v>
+      </c>
+      <c r="M21" s="3" t="s">
         <v>1248</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>1339</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>1285</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>1254</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>1249</v>
-      </c>
       <c r="N21" s="3" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="O21" s="3" t="s">
+        <v>1256</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>1247</v>
+      </c>
+      <c r="Q21" s="3" t="s">
         <v>1257</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>1248</v>
-      </c>
-      <c r="Q21" s="3" t="s">
-        <v>1258</v>
-      </c>
       <c r="R21" s="3" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="S21" s="3" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="T21" s="3" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="22" spans="1:23" ht="216">
       <c r="A22" s="3" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="C22" s="14" t="s">
         <v>1246</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="F22" s="2">
         <v>10</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="H22" s="2"/>
       <c r="I22" s="3" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>678</v>
       </c>
       <c r="K22" s="3" t="s">
+        <v>1247</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>1254</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>1298</v>
+      </c>
+      <c r="N22" s="3" t="s">
         <v>1248</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>1255</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>1299</v>
-      </c>
-      <c r="N22" s="3" t="s">
-        <v>1249</v>
-      </c>
       <c r="O22" s="3" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="P22" s="2"/>
       <c r="Q22" s="3" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="R22" s="3" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="S22" s="3" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="T22" s="3" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="U22" s="13"/>
       <c r="V22" s="12"/>
@@ -24628,56 +24805,56 @@
     </row>
     <row r="23" spans="1:23" ht="54">
       <c r="A23" s="3" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="C23" s="14" t="s">
         <v>1246</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="F23" s="2">
         <v>25</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="H23" s="2"/>
       <c r="I23" s="3" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="M23" s="3" t="s">
         <v>874</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="O23" s="3" t="s">
+        <v>1256</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>1247</v>
+      </c>
+      <c r="Q23" s="3" t="s">
         <v>1257</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>1248</v>
-      </c>
-      <c r="Q23" s="3" t="s">
-        <v>1258</v>
-      </c>
       <c r="R23" s="3" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="S23" s="3" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="T23" s="3"/>
       <c r="U23" s="12"/>
@@ -24686,56 +24863,56 @@
     </row>
     <row r="24" spans="1:23" ht="36">
       <c r="A24" s="3" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="C24" s="14" t="s">
         <v>1246</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="F24" s="2">
         <v>25</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="H24" s="2"/>
       <c r="I24" s="3" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="M24" s="3" t="s">
         <v>874</v>
       </c>
       <c r="N24" s="3" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="O24" s="3" t="s">
+        <v>1256</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>1247</v>
+      </c>
+      <c r="Q24" s="3" t="s">
         <v>1257</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>1248</v>
-      </c>
-      <c r="Q24" s="3" t="s">
-        <v>1258</v>
-      </c>
       <c r="R24" s="3" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="S24" s="3" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="T24" s="3"/>
       <c r="U24" s="12"/>
@@ -24744,872 +24921,872 @@
     </row>
     <row r="25" spans="1:23" ht="54">
       <c r="A25" s="3" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="C25" s="14" t="s">
         <v>1246</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="F25" s="2">
         <v>25</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="H25" s="2"/>
       <c r="I25" s="3" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="M25" s="3" t="s">
         <v>874</v>
       </c>
       <c r="N25" s="3" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="O25" s="3" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="P25" s="2"/>
       <c r="Q25" s="3" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="R25" s="3" t="s">
+        <v>1313</v>
+      </c>
+      <c r="S25" s="3" t="s">
+        <v>1308</v>
+      </c>
+      <c r="T25" s="3" t="s">
         <v>1314</v>
-      </c>
-      <c r="S25" s="3" t="s">
-        <v>1309</v>
-      </c>
-      <c r="T25" s="3" t="s">
-        <v>1315</v>
       </c>
     </row>
     <row r="26" spans="1:23">
       <c r="A26" s="12" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>1246</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="F26" s="13">
         <v>5</v>
       </c>
       <c r="G26" s="12" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="I26" s="12" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="J26" s="12" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="K26" s="12" t="s">
+        <v>1316</v>
+      </c>
+      <c r="L26" s="12" t="s">
+        <v>1315</v>
+      </c>
+      <c r="M26" s="12" t="s">
         <v>1317</v>
       </c>
-      <c r="L26" s="12" t="s">
-        <v>1316</v>
-      </c>
-      <c r="M26" s="12" t="s">
+      <c r="N26" s="12" t="s">
         <v>1318</v>
       </c>
-      <c r="N26" s="12" t="s">
+      <c r="O26" s="12" t="s">
+        <v>1256</v>
+      </c>
+      <c r="P26" s="13" t="s">
+        <v>1269</v>
+      </c>
+      <c r="Q26" s="12" t="s">
         <v>1319</v>
       </c>
-      <c r="O26" s="12" t="s">
-        <v>1257</v>
-      </c>
-      <c r="P26" s="13" t="s">
-        <v>1270</v>
-      </c>
-      <c r="Q26" s="12" t="s">
+      <c r="T26" s="12" t="s">
         <v>1320</v>
-      </c>
-      <c r="T26" s="12" t="s">
-        <v>1321</v>
       </c>
     </row>
     <row r="27" spans="1:23">
       <c r="A27" s="12" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>1246</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="F27" s="13">
         <v>25</v>
       </c>
       <c r="G27" s="12" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="I27" s="12" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="J27" s="12" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="K27" s="12" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="L27" s="12" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="M27" s="12" t="s">
         <v>874</v>
       </c>
       <c r="N27" s="12" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="O27" s="12" t="s">
+        <v>1256</v>
+      </c>
+      <c r="P27" s="13" t="s">
+        <v>1247</v>
+      </c>
+      <c r="Q27" s="12" t="s">
         <v>1257</v>
       </c>
-      <c r="P27" s="13" t="s">
-        <v>1248</v>
-      </c>
-      <c r="Q27" s="12" t="s">
-        <v>1258</v>
-      </c>
       <c r="R27" s="16" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="S27" s="39" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="28" spans="1:23" ht="54">
       <c r="A28" s="12" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>1246</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="F28" s="13">
         <v>0</v>
       </c>
       <c r="G28" s="12" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I28" s="12" t="s">
+        <v>1247</v>
+      </c>
+      <c r="J28" s="12" t="s">
+        <v>1262</v>
+      </c>
+      <c r="K28" s="12" t="s">
+        <v>1328</v>
+      </c>
+      <c r="L28" s="12" t="s">
+        <v>1253</v>
+      </c>
+      <c r="M28" s="12" t="s">
         <v>1248</v>
       </c>
-      <c r="J28" s="12" t="s">
-        <v>1263</v>
-      </c>
-      <c r="K28" s="12" t="s">
+      <c r="N28" s="12" t="s">
         <v>1329</v>
       </c>
-      <c r="L28" s="12" t="s">
-        <v>1254</v>
-      </c>
-      <c r="M28" s="12" t="s">
-        <v>1249</v>
-      </c>
-      <c r="N28" s="12" t="s">
-        <v>1330</v>
-      </c>
       <c r="O28" s="12" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="P28" s="13" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="Q28" s="12" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="S28" s="39" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="T28" s="34" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="29" spans="1:23" ht="54">
       <c r="A29" s="34" t="s">
+        <v>1730</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>1723</v>
+      </c>
+      <c r="D29" s="12" t="s">
         <v>1731</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="E29" s="4" t="s">
         <v>1724</v>
-      </c>
-      <c r="D29" s="12" t="s">
-        <v>1732</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>1725</v>
       </c>
       <c r="F29" s="13">
         <v>30</v>
       </c>
       <c r="G29" s="12" t="s">
-        <v>1733</v>
+        <v>1732</v>
       </c>
       <c r="I29" s="39" t="s">
+        <v>1725</v>
+      </c>
+      <c r="J29" s="12" t="s">
+        <v>1734</v>
+      </c>
+      <c r="K29" s="12" t="s">
+        <v>1735</v>
+      </c>
+      <c r="L29" s="12" t="s">
         <v>1726</v>
       </c>
-      <c r="J29" s="12" t="s">
-        <v>1735</v>
-      </c>
-      <c r="K29" s="12" t="s">
+      <c r="M29" s="12" t="s">
         <v>1736</v>
       </c>
-      <c r="L29" s="12" t="s">
-        <v>1727</v>
-      </c>
-      <c r="M29" s="12" t="s">
-        <v>1737</v>
-      </c>
       <c r="N29" s="12" t="s">
-        <v>1726</v>
+        <v>1725</v>
       </c>
       <c r="O29" s="12" t="s">
+        <v>1728</v>
+      </c>
+      <c r="P29" s="13" t="s">
+        <v>1725</v>
+      </c>
+      <c r="Q29" s="12" t="s">
         <v>1729</v>
       </c>
-      <c r="P29" s="13" t="s">
-        <v>1726</v>
-      </c>
-      <c r="Q29" s="12" t="s">
-        <v>1730</v>
-      </c>
       <c r="R29" s="12" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="S29" s="39" t="s">
-        <v>1732</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="30" spans="1:23">
       <c r="A30" s="34" t="s">
+        <v>1737</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>1723</v>
+      </c>
+      <c r="D30" s="12" t="s">
         <v>1738</v>
       </c>
-      <c r="C30" s="5" t="s">
-        <v>1724</v>
-      </c>
-      <c r="D30" s="12" t="s">
+      <c r="E30" s="4" t="s">
         <v>1739</v>
-      </c>
-      <c r="E30" s="4" t="s">
-        <v>1740</v>
       </c>
       <c r="F30" s="13">
         <v>10</v>
       </c>
       <c r="G30" s="12" t="s">
-        <v>1741</v>
+        <v>1740</v>
       </c>
       <c r="I30">
         <v>10</v>
       </c>
       <c r="J30" s="12" t="s">
+        <v>1741</v>
+      </c>
+      <c r="K30" s="12" t="s">
+        <v>1735</v>
+      </c>
+      <c r="L30" s="12" t="s">
         <v>1742</v>
       </c>
-      <c r="K30" s="12" t="s">
-        <v>1736</v>
-      </c>
-      <c r="L30" s="12" t="s">
+      <c r="M30" s="12" t="s">
+        <v>1725</v>
+      </c>
+      <c r="N30" s="12" t="s">
         <v>1743</v>
       </c>
-      <c r="M30" s="12" t="s">
-        <v>1726</v>
-      </c>
-      <c r="N30" s="12" t="s">
+      <c r="O30" s="12" t="s">
+        <v>1728</v>
+      </c>
+      <c r="Q30" s="12" t="s">
         <v>1744</v>
       </c>
-      <c r="O30" s="12" t="s">
-        <v>1729</v>
-      </c>
-      <c r="Q30" s="12" t="s">
-        <v>1745</v>
-      </c>
       <c r="S30" s="39" t="s">
-        <v>1739</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="31" spans="1:23" ht="54">
       <c r="A31" s="34" t="s">
+        <v>1745</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>1723</v>
+      </c>
+      <c r="D31" s="12" t="s">
         <v>1746</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="E31" s="4" t="s">
         <v>1724</v>
-      </c>
-      <c r="D31" s="12" t="s">
-        <v>1747</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>1725</v>
       </c>
       <c r="F31" s="13">
         <v>10</v>
       </c>
       <c r="G31" s="12" t="s">
-        <v>1734</v>
+        <v>1733</v>
       </c>
       <c r="I31" s="39" t="s">
+        <v>1725</v>
+      </c>
+      <c r="J31" s="12" t="s">
+        <v>1741</v>
+      </c>
+      <c r="K31" s="12" t="s">
+        <v>1725</v>
+      </c>
+      <c r="L31" s="12" t="s">
         <v>1726</v>
       </c>
-      <c r="J31" s="12" t="s">
-        <v>1742</v>
-      </c>
-      <c r="K31" s="12" t="s">
-        <v>1726</v>
-      </c>
-      <c r="L31" s="12" t="s">
-        <v>1727</v>
-      </c>
       <c r="M31" s="12" t="s">
+        <v>1747</v>
+      </c>
+      <c r="N31" s="12" t="s">
+        <v>1725</v>
+      </c>
+      <c r="O31" s="12" t="s">
+        <v>1728</v>
+      </c>
+      <c r="P31" s="13" t="s">
+        <v>1725</v>
+      </c>
+      <c r="Q31" s="12" t="s">
+        <v>1729</v>
+      </c>
+      <c r="S31" s="39" t="s">
+        <v>1746</v>
+      </c>
+      <c r="T31" s="34" t="s">
         <v>1748</v>
-      </c>
-      <c r="N31" s="12" t="s">
-        <v>1726</v>
-      </c>
-      <c r="O31" s="12" t="s">
-        <v>1729</v>
-      </c>
-      <c r="P31" s="13" t="s">
-        <v>1726</v>
-      </c>
-      <c r="Q31" s="12" t="s">
-        <v>1730</v>
-      </c>
-      <c r="S31" s="39" t="s">
-        <v>1747</v>
-      </c>
-      <c r="T31" s="34" t="s">
-        <v>1749</v>
       </c>
     </row>
     <row r="32" spans="1:23">
       <c r="A32" s="34" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
       <c r="C32" s="5" t="s">
+        <v>1723</v>
+      </c>
+      <c r="D32" s="12" t="s">
+        <v>1751</v>
+      </c>
+      <c r="E32" s="4" t="s">
         <v>1724</v>
-      </c>
-      <c r="D32" s="12" t="s">
-        <v>1752</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>1725</v>
       </c>
       <c r="F32" s="13">
         <v>0</v>
       </c>
       <c r="G32" s="12" t="s">
-        <v>1733</v>
+        <v>1732</v>
       </c>
       <c r="I32" s="16" t="s">
+        <v>1725</v>
+      </c>
+      <c r="J32" s="12" t="s">
+        <v>1750</v>
+      </c>
+      <c r="K32" s="12" t="s">
+        <v>1725</v>
+      </c>
+      <c r="L32" s="12" t="s">
         <v>1726</v>
       </c>
-      <c r="J32" s="12" t="s">
+      <c r="M32" s="12" t="s">
+        <v>1727</v>
+      </c>
+      <c r="N32" s="12" t="s">
+        <v>1725</v>
+      </c>
+      <c r="O32" s="12" t="s">
+        <v>1728</v>
+      </c>
+      <c r="Q32" s="12" t="s">
+        <v>1729</v>
+      </c>
+      <c r="S32" s="39" t="s">
         <v>1751</v>
       </c>
-      <c r="K32" s="12" t="s">
-        <v>1726</v>
-      </c>
-      <c r="L32" s="12" t="s">
-        <v>1727</v>
-      </c>
-      <c r="M32" s="12" t="s">
-        <v>1728</v>
-      </c>
-      <c r="N32" s="12" t="s">
-        <v>1726</v>
-      </c>
-      <c r="O32" s="12" t="s">
-        <v>1729</v>
-      </c>
-      <c r="Q32" s="12" t="s">
-        <v>1730</v>
-      </c>
-      <c r="S32" s="39" t="s">
+      <c r="T32" s="4" t="s">
         <v>1752</v>
-      </c>
-      <c r="T32" s="4" t="s">
-        <v>1753</v>
       </c>
     </row>
     <row r="33" spans="1:20" ht="54">
-      <c r="A33" s="42" t="s">
+      <c r="A33" s="34" t="s">
+        <v>1754</v>
+      </c>
+      <c r="C33" s="5" t="s">
         <v>1755</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="D33" s="12" t="s">
         <v>1756</v>
       </c>
-      <c r="D33" s="43" t="s">
-        <v>1757</v>
-      </c>
       <c r="E33" s="4" t="s">
+        <v>1758</v>
+      </c>
+      <c r="F33" s="4" t="s">
         <v>1759</v>
       </c>
-      <c r="F33" s="4" t="s">
-        <v>1760</v>
-      </c>
-      <c r="G33" s="43" t="s">
-        <v>1760</v>
+      <c r="G33" s="12" t="s">
+        <v>1759</v>
       </c>
       <c r="I33">
         <v>15</v>
       </c>
-      <c r="J33" s="43" t="s">
+      <c r="J33" s="12" t="s">
+        <v>1760</v>
+      </c>
+      <c r="K33" s="12" t="s">
         <v>1761</v>
       </c>
-      <c r="K33" s="43" t="s">
+      <c r="L33" s="12" t="s">
         <v>1762</v>
       </c>
-      <c r="L33" s="43" t="s">
+      <c r="M33" s="12" t="s">
         <v>1763</v>
       </c>
-      <c r="M33" s="43" t="s">
+      <c r="N33" s="12" t="s">
+        <v>1759</v>
+      </c>
+      <c r="O33" s="12" t="s">
         <v>1764</v>
       </c>
-      <c r="N33" s="43" t="s">
-        <v>1760</v>
-      </c>
-      <c r="O33" s="43" t="s">
-        <v>1765</v>
-      </c>
-      <c r="Q33" s="43" t="s">
-        <v>1760</v>
-      </c>
-      <c r="R33" s="43" t="s">
-        <v>1774</v>
-      </c>
-      <c r="S33" s="44" t="s">
-        <v>1757</v>
+      <c r="Q33" s="12" t="s">
+        <v>1759</v>
+      </c>
+      <c r="R33" s="12" t="s">
+        <v>1773</v>
+      </c>
+      <c r="S33" s="39" t="s">
+        <v>1756</v>
       </c>
     </row>
     <row r="34" spans="1:20">
-      <c r="A34" s="42" t="s">
+      <c r="A34" s="34" t="s">
+        <v>1774</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>1755</v>
+      </c>
+      <c r="D34" s="12" t="s">
         <v>1775</v>
       </c>
-      <c r="C34" s="5" t="s">
-        <v>1756</v>
-      </c>
-      <c r="D34" s="43" t="s">
+      <c r="E34" s="4" t="s">
+        <v>1757</v>
+      </c>
+      <c r="F34" s="42">
+        <v>5</v>
+      </c>
+      <c r="G34" s="12" t="s">
         <v>1776</v>
       </c>
-      <c r="E34" s="45" t="s">
-        <v>1758</v>
-      </c>
-      <c r="F34" s="46">
-        <v>5</v>
-      </c>
-      <c r="G34" s="43" t="s">
+      <c r="I34" s="34" t="s">
+        <v>1759</v>
+      </c>
+      <c r="J34" s="12" t="s">
         <v>1777</v>
       </c>
-      <c r="I34" s="42" t="s">
-        <v>1760</v>
-      </c>
-      <c r="J34" s="43" t="s">
+      <c r="K34" s="12" t="s">
+        <v>1759</v>
+      </c>
+      <c r="L34" s="12" t="s">
+        <v>1762</v>
+      </c>
+      <c r="M34" s="12" t="s">
         <v>1778</v>
       </c>
-      <c r="K34" s="43" t="s">
-        <v>1760</v>
-      </c>
-      <c r="L34" s="43" t="s">
-        <v>1763</v>
-      </c>
-      <c r="M34" s="43" t="s">
+      <c r="O34" s="12" t="s">
+        <v>1764</v>
+      </c>
+      <c r="Q34" s="12" t="s">
         <v>1779</v>
       </c>
-      <c r="O34" s="43" t="s">
-        <v>1765</v>
-      </c>
-      <c r="Q34" s="43" t="s">
+      <c r="S34" s="39" t="s">
+        <v>1775</v>
+      </c>
+      <c r="T34" s="4" t="s">
         <v>1780</v>
-      </c>
-      <c r="S34" s="44" t="s">
-        <v>1776</v>
-      </c>
-      <c r="T34" s="4" t="s">
-        <v>1781</v>
       </c>
     </row>
     <row r="35" spans="1:20" ht="36">
-      <c r="A35" s="42" t="s">
+      <c r="A35" s="34" t="s">
+        <v>1782</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>1755</v>
+      </c>
+      <c r="D35" s="12" t="s">
+        <v>1781</v>
+      </c>
+      <c r="E35" s="4" t="s">
         <v>1783</v>
       </c>
-      <c r="C35" s="5" t="s">
-        <v>1756</v>
-      </c>
-      <c r="D35" s="43" t="s">
-        <v>1782</v>
-      </c>
-      <c r="E35" s="45" t="s">
-        <v>1784</v>
-      </c>
       <c r="F35" s="4" t="s">
-        <v>1760</v>
-      </c>
-      <c r="G35" s="43" t="s">
-        <v>1760</v>
+        <v>1759</v>
+      </c>
+      <c r="G35" s="12" t="s">
+        <v>1759</v>
       </c>
       <c r="I35">
         <v>5</v>
       </c>
-      <c r="J35" s="43" t="s">
+      <c r="J35" s="12" t="s">
+        <v>1784</v>
+      </c>
+      <c r="K35" s="12" t="s">
         <v>1785</v>
       </c>
-      <c r="K35" s="43" t="s">
+      <c r="L35" s="12" t="s">
         <v>1786</v>
       </c>
-      <c r="L35" s="43" t="s">
+      <c r="M35" s="12" t="s">
+        <v>1759</v>
+      </c>
+      <c r="N35" s="12" t="s">
+        <v>1759</v>
+      </c>
+      <c r="O35" s="12" t="s">
+        <v>1786</v>
+      </c>
+      <c r="Q35" s="12" t="s">
+        <v>1759</v>
+      </c>
+      <c r="S35" s="39" t="s">
+        <v>1781</v>
+      </c>
+      <c r="T35" s="11" t="s">
         <v>1787</v>
-      </c>
-      <c r="M35" s="43" t="s">
-        <v>1760</v>
-      </c>
-      <c r="N35" s="43" t="s">
-        <v>1760</v>
-      </c>
-      <c r="O35" s="43" t="s">
-        <v>1787</v>
-      </c>
-      <c r="Q35" s="43" t="s">
-        <v>1760</v>
-      </c>
-      <c r="S35" s="44" t="s">
-        <v>1782</v>
-      </c>
-      <c r="T35" s="11" t="s">
-        <v>1788</v>
       </c>
     </row>
     <row r="36" spans="1:20" ht="72">
-      <c r="A36" s="42" t="s">
+      <c r="A36" s="34" t="s">
+        <v>1788</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>1755</v>
+      </c>
+      <c r="D36" s="12" t="s">
         <v>1789</v>
       </c>
-      <c r="C36" s="5" t="s">
-        <v>1756</v>
-      </c>
-      <c r="D36" s="43" t="s">
+      <c r="E36" s="4" t="s">
         <v>1790</v>
       </c>
-      <c r="E36" s="45" t="s">
-        <v>1791</v>
-      </c>
-      <c r="F36" s="46">
+      <c r="F36" s="42">
         <v>0</v>
       </c>
-      <c r="G36" s="43" t="s">
-        <v>1794</v>
+      <c r="G36" s="12" t="s">
+        <v>1793</v>
       </c>
       <c r="I36">
         <v>20</v>
       </c>
-      <c r="J36" s="43" t="s">
+      <c r="J36" s="12" t="s">
+        <v>1791</v>
+      </c>
+      <c r="K36" s="12" t="s">
+        <v>1759</v>
+      </c>
+      <c r="L36" s="12" t="s">
+        <v>1786</v>
+      </c>
+      <c r="M36" s="12" t="s">
+        <v>1759</v>
+      </c>
+      <c r="N36" s="12" t="s">
+        <v>1759</v>
+      </c>
+      <c r="O36" s="12" t="s">
+        <v>1786</v>
+      </c>
+      <c r="P36" s="12" t="s">
         <v>1792</v>
       </c>
-      <c r="K36" s="43" t="s">
-        <v>1760</v>
-      </c>
-      <c r="L36" s="43" t="s">
-        <v>1787</v>
-      </c>
-      <c r="M36" s="43" t="s">
-        <v>1760</v>
-      </c>
-      <c r="N36" s="43" t="s">
-        <v>1760</v>
-      </c>
-      <c r="O36" s="43" t="s">
-        <v>1787</v>
-      </c>
-      <c r="P36" s="43" t="s">
-        <v>1793</v>
-      </c>
-      <c r="Q36" s="43" t="s">
-        <v>1760</v>
-      </c>
-      <c r="S36" s="44" t="s">
-        <v>1790</v>
-      </c>
-      <c r="T36" s="42" t="s">
-        <v>1816</v>
+      <c r="Q36" s="12" t="s">
+        <v>1759</v>
+      </c>
+      <c r="S36" s="39" t="s">
+        <v>1789</v>
+      </c>
+      <c r="T36" s="34" t="s">
+        <v>1814</v>
       </c>
     </row>
     <row r="37" spans="1:20" ht="54">
-      <c r="A37" s="42" t="s">
-        <v>1796</v>
+      <c r="A37" s="34" t="s">
+        <v>1795</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>1756</v>
-      </c>
-      <c r="D37" s="43" t="s">
-        <v>1795</v>
-      </c>
-      <c r="E37" s="45" t="s">
-        <v>1784</v>
+        <v>1755</v>
+      </c>
+      <c r="D37" s="12" t="s">
+        <v>1794</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>1783</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>1760</v>
-      </c>
-      <c r="G37" s="43" t="s">
-        <v>1760</v>
+        <v>1759</v>
+      </c>
+      <c r="G37" s="12" t="s">
+        <v>1759</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>1760</v>
-      </c>
-      <c r="J37" s="43" t="s">
+        <v>1759</v>
+      </c>
+      <c r="J37" s="12" t="s">
+        <v>1791</v>
+      </c>
+      <c r="K37" s="12" t="s">
         <v>1792</v>
       </c>
-      <c r="K37" s="43" t="s">
-        <v>1793</v>
-      </c>
-      <c r="L37" s="43" t="s">
-        <v>1787</v>
+      <c r="L37" s="12" t="s">
+        <v>1786</v>
       </c>
       <c r="M37" s="4" t="s">
-        <v>1760</v>
-      </c>
-      <c r="N37" s="43" t="s">
-        <v>1760</v>
-      </c>
-      <c r="O37" s="43" t="s">
-        <v>1787</v>
-      </c>
-      <c r="P37" s="43" t="s">
-        <v>1760</v>
-      </c>
-      <c r="Q37" s="43" t="s">
-        <v>1760</v>
-      </c>
-      <c r="R37" s="43" t="s">
-        <v>1808</v>
-      </c>
-      <c r="S37" s="44" t="s">
-        <v>1795</v>
+        <v>1759</v>
+      </c>
+      <c r="N37" s="12" t="s">
+        <v>1759</v>
+      </c>
+      <c r="O37" s="12" t="s">
+        <v>1786</v>
+      </c>
+      <c r="P37" s="12" t="s">
+        <v>1759</v>
+      </c>
+      <c r="Q37" s="12" t="s">
+        <v>1759</v>
+      </c>
+      <c r="R37" s="12" t="s">
+        <v>1806</v>
+      </c>
+      <c r="S37" s="39" t="s">
+        <v>1794</v>
       </c>
     </row>
     <row r="38" spans="1:20" ht="36">
-      <c r="A38" s="42" t="s">
-        <v>1809</v>
+      <c r="A38" s="34" t="s">
+        <v>1807</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>1756</v>
-      </c>
-      <c r="D38" s="43" t="s">
-        <v>1810</v>
-      </c>
-      <c r="E38" s="45" t="s">
-        <v>1758</v>
+        <v>1755</v>
+      </c>
+      <c r="D38" s="12" t="s">
+        <v>1808</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>1757</v>
       </c>
       <c r="F38">
         <v>40</v>
       </c>
-      <c r="G38" s="43" t="s">
+      <c r="G38" s="12" t="s">
+        <v>1809</v>
+      </c>
+      <c r="I38" s="4" t="s">
+        <v>1759</v>
+      </c>
+      <c r="J38" s="12" t="s">
+        <v>1760</v>
+      </c>
+      <c r="K38" s="12" t="s">
+        <v>1759</v>
+      </c>
+      <c r="L38" s="12" t="s">
+        <v>1762</v>
+      </c>
+      <c r="M38" s="12" t="s">
+        <v>1810</v>
+      </c>
+      <c r="N38" s="12" t="s">
+        <v>1759</v>
+      </c>
+      <c r="O38" s="12" t="s">
+        <v>1764</v>
+      </c>
+      <c r="Q38" s="12" t="s">
+        <v>1779</v>
+      </c>
+      <c r="R38" s="11" t="s">
         <v>1811</v>
       </c>
-      <c r="I38" s="4" t="s">
-        <v>1760</v>
-      </c>
-      <c r="J38" s="43" t="s">
-        <v>1761</v>
-      </c>
-      <c r="K38" s="43" t="s">
-        <v>1760</v>
-      </c>
-      <c r="L38" s="43" t="s">
-        <v>1763</v>
-      </c>
-      <c r="M38" s="43" t="s">
-        <v>1812</v>
-      </c>
-      <c r="N38" s="43" t="s">
-        <v>1760</v>
-      </c>
-      <c r="O38" s="43" t="s">
-        <v>1765</v>
-      </c>
-      <c r="Q38" s="43" t="s">
-        <v>1780</v>
-      </c>
-      <c r="R38" s="11" t="s">
-        <v>1813</v>
-      </c>
-      <c r="S38" s="44" t="s">
-        <v>1810</v>
+      <c r="S38" s="39" t="s">
+        <v>1808</v>
       </c>
     </row>
     <row r="39" spans="1:20" ht="54">
-      <c r="A39" s="42" t="s">
-        <v>1815</v>
+      <c r="A39" s="34" t="s">
+        <v>1813</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>1756</v>
-      </c>
-      <c r="D39" s="43" t="s">
-        <v>1814</v>
-      </c>
-      <c r="E39" s="45" t="s">
-        <v>1791</v>
+        <v>1755</v>
+      </c>
+      <c r="D39" s="12" t="s">
+        <v>1812</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>1790</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>1760</v>
-      </c>
-      <c r="G39" s="43" t="s">
-        <v>1818</v>
+        <v>1759</v>
+      </c>
+      <c r="G39" s="12" t="s">
+        <v>1816</v>
       </c>
       <c r="I39" s="4" t="s">
-        <v>1760</v>
-      </c>
-      <c r="J39" s="43" t="s">
-        <v>1827</v>
-      </c>
-      <c r="K39" s="43" t="s">
-        <v>1760</v>
-      </c>
-      <c r="L39" s="43" t="s">
-        <v>1787</v>
-      </c>
-      <c r="M39" s="43" t="s">
-        <v>1760</v>
-      </c>
-      <c r="N39" s="43" t="s">
-        <v>1760</v>
-      </c>
-      <c r="O39" s="43" t="s">
-        <v>1787</v>
-      </c>
-      <c r="P39" s="43" t="s">
-        <v>1760</v>
-      </c>
-      <c r="Q39" s="43" t="s">
-        <v>1760</v>
-      </c>
-      <c r="S39" s="44" t="s">
-        <v>1814</v>
-      </c>
-      <c r="T39" s="42" t="s">
-        <v>1819</v>
+        <v>1759</v>
+      </c>
+      <c r="J39" s="12" t="s">
+        <v>1825</v>
+      </c>
+      <c r="K39" s="12" t="s">
+        <v>1759</v>
+      </c>
+      <c r="L39" s="12" t="s">
+        <v>1786</v>
+      </c>
+      <c r="M39" s="12" t="s">
+        <v>1759</v>
+      </c>
+      <c r="N39" s="12" t="s">
+        <v>1759</v>
+      </c>
+      <c r="O39" s="12" t="s">
+        <v>1786</v>
+      </c>
+      <c r="P39" s="12" t="s">
+        <v>1759</v>
+      </c>
+      <c r="Q39" s="12" t="s">
+        <v>1759</v>
+      </c>
+      <c r="S39" s="39" t="s">
+        <v>1812</v>
+      </c>
+      <c r="T39" s="34" t="s">
+        <v>1817</v>
       </c>
     </row>
     <row r="40" spans="1:20" ht="36">
-      <c r="A40" s="42" t="s">
-        <v>1820</v>
+      <c r="A40" s="34" t="s">
+        <v>1818</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>1756</v>
-      </c>
-      <c r="D40" s="43" t="s">
-        <v>1817</v>
-      </c>
-      <c r="E40" s="45" t="s">
-        <v>1758</v>
+        <v>1755</v>
+      </c>
+      <c r="D40" s="12" t="s">
+        <v>1815</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>1757</v>
       </c>
       <c r="F40">
         <v>0</v>
       </c>
-      <c r="G40" s="43" t="s">
+      <c r="G40" s="12" t="s">
+        <v>1819</v>
+      </c>
+      <c r="I40" s="4" t="s">
+        <v>1822</v>
+      </c>
+      <c r="J40" s="12" t="s">
+        <v>1791</v>
+      </c>
+      <c r="K40" s="12" t="s">
+        <v>1792</v>
+      </c>
+      <c r="L40" s="12" t="s">
+        <v>1762</v>
+      </c>
+      <c r="M40" s="12" t="s">
+        <v>1820</v>
+      </c>
+      <c r="N40" s="12" t="s">
+        <v>1759</v>
+      </c>
+      <c r="O40" s="12" t="s">
+        <v>1764</v>
+      </c>
+      <c r="P40" s="12" t="s">
+        <v>1759</v>
+      </c>
+      <c r="Q40" s="12" t="s">
         <v>1821</v>
       </c>
-      <c r="I40" s="4" t="s">
-        <v>1824</v>
-      </c>
-      <c r="J40" s="43" t="s">
-        <v>1792</v>
-      </c>
-      <c r="K40" s="43" t="s">
-        <v>1793</v>
-      </c>
-      <c r="L40" s="43" t="s">
-        <v>1763</v>
-      </c>
-      <c r="M40" s="43" t="s">
-        <v>1822</v>
-      </c>
-      <c r="N40" s="43" t="s">
-        <v>1760</v>
-      </c>
-      <c r="O40" s="43" t="s">
-        <v>1765</v>
-      </c>
-      <c r="P40" s="43" t="s">
-        <v>1760</v>
-      </c>
-      <c r="Q40" s="43" t="s">
-        <v>1823</v>
-      </c>
-      <c r="S40" s="44" t="s">
-        <v>1817</v>
+      <c r="S40" s="39" t="s">
+        <v>1815</v>
       </c>
     </row>
     <row r="41" spans="1:20" ht="36">
-      <c r="A41" s="42" t="s">
+      <c r="A41" s="34" t="s">
+        <v>1824</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>1755</v>
+      </c>
+      <c r="D41" s="12" t="s">
+        <v>1823</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>1757</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>1759</v>
+      </c>
+      <c r="G41" s="12" t="s">
+        <v>1759</v>
+      </c>
+      <c r="I41" s="4" t="s">
+        <v>1759</v>
+      </c>
+      <c r="J41" s="12" t="s">
+        <v>1784</v>
+      </c>
+      <c r="K41" s="12" t="s">
+        <v>1759</v>
+      </c>
+      <c r="L41" s="12" t="s">
+        <v>1762</v>
+      </c>
+      <c r="M41" s="12" t="s">
         <v>1826</v>
       </c>
-      <c r="C41" s="5" t="s">
-        <v>1756</v>
-      </c>
-      <c r="D41" s="43" t="s">
-        <v>1825</v>
-      </c>
-      <c r="E41" s="45" t="s">
-        <v>1758</v>
-      </c>
-      <c r="F41" s="4" t="s">
-        <v>1760</v>
-      </c>
-      <c r="G41" s="43" t="s">
-        <v>1760</v>
-      </c>
-      <c r="I41" s="4" t="s">
-        <v>1760</v>
-      </c>
-      <c r="J41" s="43" t="s">
-        <v>1785</v>
-      </c>
-      <c r="K41" s="43" t="s">
-        <v>1760</v>
-      </c>
-      <c r="L41" s="43" t="s">
-        <v>1763</v>
-      </c>
-      <c r="M41" s="43" t="s">
-        <v>1828</v>
-      </c>
-      <c r="N41" s="43" t="s">
-        <v>1760</v>
-      </c>
-      <c r="O41" s="43" t="s">
-        <v>1765</v>
-      </c>
-      <c r="Q41" s="43" t="s">
+      <c r="N41" s="12" t="s">
+        <v>1759</v>
+      </c>
+      <c r="O41" s="12" t="s">
+        <v>1764</v>
+      </c>
+      <c r="Q41" s="12" t="s">
+        <v>1821</v>
+      </c>
+      <c r="R41" s="11" t="s">
+        <v>1811</v>
+      </c>
+      <c r="S41" s="39" t="s">
         <v>1823</v>
-      </c>
-      <c r="R41" s="11" t="s">
-        <v>1813</v>
-      </c>
-      <c r="S41" s="44" t="s">
-        <v>1825</v>
       </c>
     </row>
   </sheetData>
@@ -25621,19 +25798,20 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="21.8984375" customWidth="1"/>
     <col min="2" max="2" width="15.296875" customWidth="1"/>
     <col min="3" max="3" width="17.3984375" customWidth="1"/>
     <col min="4" max="4" width="10.59765625" customWidth="1"/>
-    <col min="5" max="5" width="79" customWidth="1"/>
-    <col min="6" max="6" width="62.59765625" customWidth="1"/>
-    <col min="7" max="7" width="101.19921875" customWidth="1"/>
+    <col min="5" max="5" width="10.3984375" customWidth="1"/>
+    <col min="6" max="6" width="79" customWidth="1"/>
+    <col min="7" max="7" width="62.59765625" customWidth="1"/>
+    <col min="8" max="8" width="101.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
@@ -25647,39 +25825,45 @@
         <v>722</v>
       </c>
       <c r="E1" s="10" t="s">
+        <v>1852</v>
+      </c>
+      <c r="F1" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="G1" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="H1" s="10" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="36">
+    <row r="2" spans="1:8" ht="36">
       <c r="A2" s="4" t="s">
+        <v>1505</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>1506</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>1507</v>
-      </c>
       <c r="C2" s="4" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>1216</v>
       </c>
       <c r="E2" s="11" t="s">
+        <v>1853</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>1507</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>1508</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>1509</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>1509</v>
+      <c r="H2" s="4" t="s">
+        <v>1508</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="37.200000000000003" customHeight="1">
+    <row r="3" spans="1:8" ht="37.200000000000003" customHeight="1">
       <c r="A3" s="4" t="s">
         <v>261</v>
       </c>
@@ -25693,16 +25877,19 @@
         <v>188</v>
       </c>
       <c r="E3" s="3" t="s">
+        <v>1854</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="G3" s="11" t="s">
         <v>260</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="H3" s="3" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="36">
+    <row r="4" spans="1:8" ht="36">
       <c r="A4" s="4" t="s">
         <v>262</v>
       </c>
@@ -25716,16 +25903,19 @@
         <v>188</v>
       </c>
       <c r="E4" s="3" t="s">
+        <v>1854</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="G4" s="11" t="s">
         <v>259</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="H4" s="11" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="54">
+    <row r="5" spans="1:8" ht="54">
       <c r="A5" s="4" t="s">
         <v>263</v>
       </c>
@@ -25739,16 +25929,19 @@
         <v>188</v>
       </c>
       <c r="E5" s="11" t="s">
+        <v>1854</v>
+      </c>
+      <c r="F5" s="11" t="s">
         <v>256</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="G5" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="H5" s="4" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:8">
       <c r="A6" s="4" t="s">
         <v>278</v>
       </c>
@@ -25762,16 +25955,19 @@
         <v>188</v>
       </c>
       <c r="E6" s="4" t="s">
+        <v>1854</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="G6" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="H6" s="4" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="36">
+    <row r="7" spans="1:8" ht="36">
       <c r="A7" s="4" t="s">
         <v>323</v>
       </c>
@@ -25785,16 +25981,19 @@
         <v>188</v>
       </c>
       <c r="E7" s="11" t="s">
+        <v>1854</v>
+      </c>
+      <c r="F7" s="11" t="s">
         <v>666</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="G7" s="4" t="s">
         <v>478</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="H7" s="4" t="s">
         <v>667</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="36">
+    <row r="8" spans="1:8" ht="36">
       <c r="A8" s="4" t="s">
         <v>660</v>
       </c>
@@ -25808,16 +26007,19 @@
         <v>723</v>
       </c>
       <c r="E8" s="11" t="s">
+        <v>1854</v>
+      </c>
+      <c r="F8" s="11" t="s">
         <v>663</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="G8" s="4" t="s">
         <v>664</v>
       </c>
-      <c r="G8" s="11" t="s">
+      <c r="H8" s="11" t="s">
         <v>665</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:8">
       <c r="A9" s="4" t="s">
         <v>1164</v>
       </c>
@@ -25831,16 +26033,19 @@
         <v>723</v>
       </c>
       <c r="E9" s="11" t="s">
+        <v>1854</v>
+      </c>
+      <c r="F9" s="11" t="s">
         <v>703</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="G9" s="4" t="s">
         <v>704</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="H9" s="4" t="s">
         <v>705</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="36">
+    <row r="10" spans="1:8" ht="36">
       <c r="A10" s="4" t="s">
         <v>1214</v>
       </c>
@@ -25854,16 +26059,19 @@
         <v>1216</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>1754</v>
-      </c>
-      <c r="F10" s="4" t="s">
+        <v>1854</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>1753</v>
+      </c>
+      <c r="G10" s="4" t="s">
         <v>1222</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="H10" s="4" t="s">
         <v>1223</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="54">
+    <row r="11" spans="1:8" ht="54">
       <c r="A11" s="4" t="s">
         <v>1217</v>
       </c>
@@ -25877,16 +26085,19 @@
         <v>1216</v>
       </c>
       <c r="E11" s="11" t="s">
+        <v>1854</v>
+      </c>
+      <c r="F11" s="11" t="s">
         <v>1219</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="G11" s="4" t="s">
         <v>1220</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="H11" s="4" t="s">
         <v>1221</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="126">
+    <row r="12" spans="1:8" ht="126">
       <c r="A12" s="4" t="s">
         <v>1210</v>
       </c>
@@ -25900,16 +26111,19 @@
         <v>188</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>1296</v>
-      </c>
-      <c r="F12" s="4" t="s">
+        <v>1854</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>1295</v>
+      </c>
+      <c r="G12" s="4" t="s">
         <v>1212</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="H12" s="4" t="s">
         <v>1213</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="90">
+    <row r="13" spans="1:8" ht="90">
       <c r="A13" s="4" t="s">
         <v>1225</v>
       </c>
@@ -25923,16 +26137,19 @@
         <v>188</v>
       </c>
       <c r="E13" s="11" t="s">
+        <v>1854</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>1303</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>1229</v>
+      </c>
+      <c r="H13" s="11" t="s">
         <v>1304</v>
       </c>
-      <c r="F13" s="11" t="s">
-        <v>1229</v>
-      </c>
-      <c r="G13" s="11" t="s">
-        <v>1305</v>
-      </c>
     </row>
-    <row r="14" spans="1:7" ht="36">
+    <row r="14" spans="1:8" ht="36">
       <c r="A14" s="4" t="s">
         <v>1226</v>
       </c>
@@ -25946,12 +26163,15 @@
         <v>188</v>
       </c>
       <c r="E14" s="11" t="s">
+        <v>1854</v>
+      </c>
+      <c r="F14" s="11" t="s">
         <v>1238</v>
       </c>
-      <c r="F14" s="4"/>
       <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:8">
       <c r="A15" s="4" t="s">
         <v>1239</v>
       </c>
@@ -25965,21 +26185,24 @@
         <v>188</v>
       </c>
       <c r="E15" s="11" t="s">
+        <v>1854</v>
+      </c>
+      <c r="F15" s="11" t="s">
         <v>1241</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="G15" s="4" t="s">
         <v>1243</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="H15" s="4" t="s">
         <v>1242</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="54">
+    <row r="16" spans="1:8" ht="54">
       <c r="A16" s="4" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>1228</v>
@@ -25988,40 +26211,46 @@
         <v>188</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>1422</v>
-      </c>
-      <c r="F16" s="4"/>
+        <v>1854</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>1421</v>
+      </c>
       <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
     </row>
-    <row r="17" spans="1:7" ht="54">
+    <row r="17" spans="1:8" ht="54">
       <c r="A17" s="4" t="s">
+        <v>1419</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>1418</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>1420</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>1419</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>1421</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>188</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>1493</v>
+        <v>1854</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>1425</v>
-      </c>
-      <c r="G17" s="4" t="s">
+        <v>1492</v>
+      </c>
+      <c r="G17" s="11" t="s">
         <v>1424</v>
       </c>
+      <c r="H17" s="4" t="s">
+        <v>1423</v>
+      </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:8">
       <c r="A18" s="4" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>286</v>
@@ -26030,21 +26259,24 @@
         <v>188</v>
       </c>
       <c r="E18" s="11" t="s">
+        <v>1854</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>1425</v>
+      </c>
+      <c r="G18" s="4" t="s">
         <v>1426</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="H18" s="4" t="s">
         <v>1427</v>
       </c>
-      <c r="G18" s="4" t="s">
-        <v>1428</v>
-      </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:8">
       <c r="A19" s="4" t="s">
+        <v>1511</v>
+      </c>
+      <c r="B19" s="4" t="s">
         <v>1512</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>1513</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>702</v>
@@ -26053,21 +26285,24 @@
         <v>188</v>
       </c>
       <c r="E19" s="11" t="s">
+        <v>1854</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>1513</v>
+      </c>
+      <c r="G19" s="4" t="s">
         <v>1514</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="H19" s="4" t="s">
         <v>1515</v>
       </c>
-      <c r="G19" s="4" t="s">
-        <v>1516</v>
-      </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:8">
       <c r="A20" s="4" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>702</v>
@@ -26076,21 +26311,24 @@
         <v>188</v>
       </c>
       <c r="E20" s="11" t="s">
+        <v>1854</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>1526</v>
+      </c>
+      <c r="G20" s="4" t="s">
         <v>1527</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="H20" s="4" t="s">
         <v>1528</v>
       </c>
-      <c r="G20" s="4" t="s">
-        <v>1529</v>
-      </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:8">
       <c r="A21" s="4" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>702</v>
@@ -26099,21 +26337,24 @@
         <v>188</v>
       </c>
       <c r="E21" s="11" t="s">
+        <v>1854</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>1538</v>
+      </c>
+      <c r="G21" s="4" t="s">
         <v>1539</v>
       </c>
-      <c r="F21" s="4" t="s">
+      <c r="H21" s="4" t="s">
         <v>1540</v>
       </c>
-      <c r="G21" s="4" t="s">
-        <v>1541</v>
-      </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:8">
       <c r="A22" s="4" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>286</v>
@@ -26122,44 +26363,50 @@
         <v>188</v>
       </c>
       <c r="E22" s="11" t="s">
+        <v>1854</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>1584</v>
+      </c>
+      <c r="G22" s="4" t="s">
         <v>1585</v>
       </c>
-      <c r="F22" s="4" t="s">
+      <c r="H22" s="4" t="s">
         <v>1586</v>
       </c>
-      <c r="G22" s="4" t="s">
-        <v>1587</v>
-      </c>
     </row>
-    <row r="23" spans="1:7" ht="144">
+    <row r="23" spans="1:8" ht="144">
       <c r="A23" s="11" t="s">
+        <v>1602</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>1601</v>
+      </c>
+      <c r="C23" s="4" t="s">
         <v>1603</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>1602</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>1604</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>188</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>1607</v>
+        <v>1854</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>1609</v>
+        <v>1606</v>
       </c>
       <c r="G23" s="11" t="s">
-        <v>1605</v>
+        <v>1608</v>
+      </c>
+      <c r="H23" s="11" t="s">
+        <v>1604</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:8">
       <c r="A24" s="4" t="s">
+        <v>1613</v>
+      </c>
+      <c r="B24" s="4" t="s">
         <v>1614</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>1615</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>702</v>
@@ -26168,21 +26415,24 @@
         <v>188</v>
       </c>
       <c r="E24" s="11" t="s">
+        <v>1854</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>1765</v>
+      </c>
+      <c r="G24" s="4" t="s">
         <v>1766</v>
       </c>
-      <c r="F24" s="4" t="s">
+      <c r="H24" s="4" t="s">
         <v>1767</v>
       </c>
-      <c r="G24" s="4" t="s">
-        <v>1768</v>
-      </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:8">
       <c r="A25" s="4" t="s">
+        <v>1663</v>
+      </c>
+      <c r="B25" s="4" t="s">
         <v>1664</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>1665</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>286</v>
@@ -26191,21 +26441,24 @@
         <v>188</v>
       </c>
       <c r="E25" s="11" t="s">
+        <v>1854</v>
+      </c>
+      <c r="F25" s="11" t="s">
+        <v>1665</v>
+      </c>
+      <c r="G25" s="4" t="s">
         <v>1666</v>
       </c>
-      <c r="F25" s="4" t="s">
+      <c r="H25" s="4" t="s">
         <v>1667</v>
       </c>
-      <c r="G25" s="4" t="s">
-        <v>1668</v>
-      </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:8">
       <c r="A26" s="4" t="s">
+        <v>1768</v>
+      </c>
+      <c r="B26" s="4" t="s">
         <v>1769</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>1770</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>702</v>
@@ -26214,59 +26467,68 @@
         <v>188</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>1773</v>
-      </c>
-      <c r="F26" s="4" t="s">
+        <v>1854</v>
+      </c>
+      <c r="F26" s="11" t="s">
+        <v>1772</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>1770</v>
+      </c>
+      <c r="H26" s="4" t="s">
         <v>1771</v>
       </c>
-      <c r="G26" s="4" t="s">
-        <v>1772</v>
-      </c>
     </row>
-    <row r="27" spans="1:7" ht="36">
+    <row r="27" spans="1:8" ht="36">
       <c r="A27" s="4" t="s">
+        <v>1797</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>1796</v>
+      </c>
+      <c r="C27" s="4" t="s">
         <v>1798</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>1797</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>1799</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>188</v>
       </c>
       <c r="E27" s="11" t="s">
+        <v>1853</v>
+      </c>
+      <c r="F27" s="11" t="s">
+        <v>1855</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>1799</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>1799</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="36">
+      <c r="A28" s="4" t="s">
+        <v>1801</v>
+      </c>
+      <c r="B28" s="4" t="s">
         <v>1800</v>
       </c>
-      <c r="F27" s="4" t="s">
-        <v>1801</v>
-      </c>
-      <c r="G27" s="4" t="s">
-        <v>1801</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="36">
-      <c r="A28" s="4" t="s">
-        <v>1803</v>
-      </c>
-      <c r="B28" s="4" t="s">
+      <c r="C28" s="4" t="s">
         <v>1802</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>1804</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>188</v>
       </c>
       <c r="E28" s="11" t="s">
+        <v>1854</v>
+      </c>
+      <c r="F28" s="11" t="s">
+        <v>1803</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>1804</v>
+      </c>
+      <c r="H28" s="4" t="s">
         <v>1805</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>1806</v>
-      </c>
-      <c r="G28" s="4" t="s">
-        <v>1807</v>
       </c>
     </row>
   </sheetData>
@@ -26278,7 +26540,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AS14"/>
+  <dimension ref="A1:AS20"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -26339,7 +26601,7 @@
         <v>91</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>443</v>
@@ -27528,7 +27790,7 @@
         <v>130</v>
       </c>
       <c r="I14" s="13">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="J14" s="13">
         <v>120</v>
@@ -27561,7 +27823,7 @@
         <v>0.5</v>
       </c>
       <c r="T14" s="12" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="U14" s="33">
         <v>0</v>
@@ -27570,19 +27832,484 @@
         <v>0</v>
       </c>
       <c r="W14" s="12" t="s">
+        <v>1866</v>
+      </c>
+      <c r="X14" s="12" t="s">
         <v>1247</v>
       </c>
-      <c r="X14" s="12" t="s">
-        <v>1248</v>
-      </c>
       <c r="Y14" s="16" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="Z14" s="34" t="s">
+        <v>1493</v>
+      </c>
+      <c r="AB14" s="34" t="s">
         <v>1494</v>
       </c>
-      <c r="AB14" s="34" t="s">
-        <v>1495</v>
+    </row>
+    <row r="15" spans="1:45">
+      <c r="A15" s="39" t="s">
+        <v>1832</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>1827</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>1840</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>1841</v>
+      </c>
+      <c r="E15" s="13">
+        <v>630</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15" s="13">
+        <v>130</v>
+      </c>
+      <c r="H15" s="13">
+        <v>80</v>
+      </c>
+      <c r="I15" s="13">
+        <v>110</v>
+      </c>
+      <c r="J15" s="13">
+        <v>100</v>
+      </c>
+      <c r="K15" s="33">
+        <v>0</v>
+      </c>
+      <c r="L15" s="33">
+        <v>0.5</v>
+      </c>
+      <c r="M15" s="33">
+        <v>0</v>
+      </c>
+      <c r="N15" s="33">
+        <v>0</v>
+      </c>
+      <c r="O15" s="33">
+        <v>0</v>
+      </c>
+      <c r="P15" s="33">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="33">
+        <v>1</v>
+      </c>
+      <c r="R15" s="33">
+        <v>0</v>
+      </c>
+      <c r="S15" s="33">
+        <v>0.5</v>
+      </c>
+      <c r="T15" s="12" t="s">
+        <v>1843</v>
+      </c>
+      <c r="U15" s="33">
+        <v>0</v>
+      </c>
+      <c r="V15" s="33">
+        <v>0</v>
+      </c>
+      <c r="W15" s="12" t="s">
+        <v>1849</v>
+      </c>
+      <c r="X15" s="12" t="s">
+        <v>1842</v>
+      </c>
+      <c r="Z15" s="34" t="s">
+        <v>1860</v>
+      </c>
+    </row>
+    <row r="16" spans="1:45" ht="54">
+      <c r="A16" s="39" t="s">
+        <v>1833</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>1828</v>
+      </c>
+      <c r="C16" t="s">
+        <v>1839</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>1841</v>
+      </c>
+      <c r="E16" s="13">
+        <v>580</v>
+      </c>
+      <c r="F16">
+        <v>20</v>
+      </c>
+      <c r="G16" s="13">
+        <v>110</v>
+      </c>
+      <c r="H16" s="13">
+        <v>110</v>
+      </c>
+      <c r="I16" s="13">
+        <v>100</v>
+      </c>
+      <c r="J16" s="13">
+        <v>100</v>
+      </c>
+      <c r="K16" s="33">
+        <v>0</v>
+      </c>
+      <c r="L16" s="33">
+        <v>0.5</v>
+      </c>
+      <c r="M16" s="33">
+        <v>0</v>
+      </c>
+      <c r="N16" s="33">
+        <v>0</v>
+      </c>
+      <c r="O16" s="33">
+        <v>0</v>
+      </c>
+      <c r="P16" s="33">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="33">
+        <v>1</v>
+      </c>
+      <c r="R16" s="33">
+        <v>0</v>
+      </c>
+      <c r="S16" s="33">
+        <v>0.5</v>
+      </c>
+      <c r="T16" s="12" t="s">
+        <v>1844</v>
+      </c>
+      <c r="U16" s="33">
+        <v>0</v>
+      </c>
+      <c r="V16" s="33">
+        <v>0</v>
+      </c>
+      <c r="W16" s="12" t="s">
+        <v>1849</v>
+      </c>
+      <c r="X16" s="12" t="s">
+        <v>1845</v>
+      </c>
+      <c r="Z16" s="34" t="s">
+        <v>1861</v>
+      </c>
+    </row>
+    <row r="17" spans="1:26">
+      <c r="A17" s="39" t="s">
+        <v>1835</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>1834</v>
+      </c>
+      <c r="C17" t="s">
+        <v>1839</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>1841</v>
+      </c>
+      <c r="E17" s="13">
+        <v>600</v>
+      </c>
+      <c r="F17">
+        <v>30</v>
+      </c>
+      <c r="G17" s="13">
+        <v>100</v>
+      </c>
+      <c r="H17" s="13">
+        <v>120</v>
+      </c>
+      <c r="I17" s="13">
+        <v>105</v>
+      </c>
+      <c r="J17" s="13">
+        <v>110</v>
+      </c>
+      <c r="K17" s="33">
+        <v>0</v>
+      </c>
+      <c r="L17" s="33">
+        <v>0.5</v>
+      </c>
+      <c r="M17" s="33">
+        <v>0</v>
+      </c>
+      <c r="N17" s="33">
+        <v>0</v>
+      </c>
+      <c r="O17" s="33">
+        <v>0</v>
+      </c>
+      <c r="P17" s="33">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="33">
+        <v>1</v>
+      </c>
+      <c r="R17" s="33">
+        <v>0</v>
+      </c>
+      <c r="S17" s="33">
+        <v>0.5</v>
+      </c>
+      <c r="T17" s="12" t="s">
+        <v>1842</v>
+      </c>
+      <c r="U17" s="33">
+        <v>0</v>
+      </c>
+      <c r="V17" s="33">
+        <v>0</v>
+      </c>
+      <c r="W17" s="12" t="s">
+        <v>1846</v>
+      </c>
+      <c r="X17" s="12" t="s">
+        <v>1847</v>
+      </c>
+      <c r="Z17" s="34" t="s">
+        <v>1862</v>
+      </c>
+    </row>
+    <row r="18" spans="1:26" ht="36">
+      <c r="A18" s="39" t="s">
+        <v>1836</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>1829</v>
+      </c>
+      <c r="C18" t="s">
+        <v>1839</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>1841</v>
+      </c>
+      <c r="E18" s="13">
+        <v>750</v>
+      </c>
+      <c r="F18">
+        <v>100</v>
+      </c>
+      <c r="G18" s="13">
+        <v>140</v>
+      </c>
+      <c r="H18" s="13">
+        <v>50</v>
+      </c>
+      <c r="I18" s="13">
+        <v>140</v>
+      </c>
+      <c r="J18" s="13">
+        <v>70</v>
+      </c>
+      <c r="K18" s="33">
+        <v>0</v>
+      </c>
+      <c r="L18" s="33">
+        <v>0.5</v>
+      </c>
+      <c r="M18" s="33">
+        <v>0</v>
+      </c>
+      <c r="N18" s="33">
+        <v>0</v>
+      </c>
+      <c r="O18" s="33">
+        <v>0</v>
+      </c>
+      <c r="P18" s="33">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="33">
+        <v>1</v>
+      </c>
+      <c r="R18" s="33">
+        <v>0</v>
+      </c>
+      <c r="S18" s="33">
+        <v>0.5</v>
+      </c>
+      <c r="T18" s="12" t="s">
+        <v>1848</v>
+      </c>
+      <c r="U18" s="33">
+        <v>0</v>
+      </c>
+      <c r="V18" s="33">
+        <v>0</v>
+      </c>
+      <c r="W18" s="12" t="s">
+        <v>654</v>
+      </c>
+      <c r="X18" s="12" t="s">
+        <v>1842</v>
+      </c>
+      <c r="Z18" s="34" t="s">
+        <v>1863</v>
+      </c>
+    </row>
+    <row r="19" spans="1:26">
+      <c r="A19" s="4" t="s">
+        <v>1837</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>1830</v>
+      </c>
+      <c r="C19" t="s">
+        <v>1839</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>1841</v>
+      </c>
+      <c r="E19" s="13">
+        <v>620</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19" s="13">
+        <v>120</v>
+      </c>
+      <c r="H19" s="13">
+        <v>100</v>
+      </c>
+      <c r="I19" s="13">
+        <v>110</v>
+      </c>
+      <c r="J19" s="13">
+        <v>120</v>
+      </c>
+      <c r="K19" s="33">
+        <v>0</v>
+      </c>
+      <c r="L19" s="33">
+        <v>0.5</v>
+      </c>
+      <c r="M19" s="33">
+        <v>0</v>
+      </c>
+      <c r="N19" s="33">
+        <v>0</v>
+      </c>
+      <c r="O19" s="33">
+        <v>0</v>
+      </c>
+      <c r="P19" s="33">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="33">
+        <v>1</v>
+      </c>
+      <c r="R19" s="33">
+        <v>0</v>
+      </c>
+      <c r="S19" s="33">
+        <v>0.5</v>
+      </c>
+      <c r="T19" s="12" t="s">
+        <v>1850</v>
+      </c>
+      <c r="U19" s="33">
+        <v>0</v>
+      </c>
+      <c r="V19" s="33">
+        <v>0</v>
+      </c>
+      <c r="W19" s="12" t="s">
+        <v>1851</v>
+      </c>
+      <c r="X19" s="12" t="s">
+        <v>1847</v>
+      </c>
+      <c r="Z19" s="34" t="s">
+        <v>1864</v>
+      </c>
+    </row>
+    <row r="20" spans="1:26" ht="36">
+      <c r="A20" s="39" t="s">
+        <v>1838</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>1831</v>
+      </c>
+      <c r="C20" t="s">
+        <v>1839</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>1841</v>
+      </c>
+      <c r="E20" s="13">
+        <v>700</v>
+      </c>
+      <c r="F20" s="42" t="s">
+        <v>1856</v>
+      </c>
+      <c r="G20" s="13">
+        <v>50</v>
+      </c>
+      <c r="H20" s="13">
+        <v>130</v>
+      </c>
+      <c r="I20" s="13">
+        <v>110</v>
+      </c>
+      <c r="J20" s="13">
+        <v>100</v>
+      </c>
+      <c r="K20" s="33">
+        <v>0</v>
+      </c>
+      <c r="L20" s="33">
+        <v>0.5</v>
+      </c>
+      <c r="M20" s="33">
+        <v>0</v>
+      </c>
+      <c r="N20" s="33">
+        <v>0</v>
+      </c>
+      <c r="O20" s="33">
+        <v>0</v>
+      </c>
+      <c r="P20" s="33">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="33">
+        <v>1</v>
+      </c>
+      <c r="R20" s="33">
+        <v>0</v>
+      </c>
+      <c r="S20" s="33">
+        <v>0.5</v>
+      </c>
+      <c r="T20" s="12" t="s">
+        <v>1857</v>
+      </c>
+      <c r="U20" s="33">
+        <v>0</v>
+      </c>
+      <c r="V20" s="33">
+        <v>0</v>
+      </c>
+      <c r="W20" s="12" t="s">
+        <v>653</v>
+      </c>
+      <c r="X20" s="12" t="s">
+        <v>1858</v>
+      </c>
+      <c r="Y20" s="34" t="s">
+        <v>1859</v>
+      </c>
+      <c r="Z20" s="34" t="s">
+        <v>1865</v>
       </c>
     </row>
   </sheetData>
@@ -28646,7 +29373,7 @@
         <v>1140</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="G31" s="4" t="s">
         <v>1148</v>
@@ -28678,7 +29405,7 @@
         <v>1140</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="G32" s="4" t="s">
         <v>1149</v>
@@ -28692,205 +29419,205 @@
     </row>
     <row r="33" spans="1:10" ht="54">
       <c r="A33" s="4" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="D33" s="7" t="s">
         <v>518</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="G33" s="4" t="s">
         <v>1018</v>
       </c>
       <c r="I33" s="12" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="J33" s="11" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="54">
       <c r="A34" s="4" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="D34" s="7" t="s">
         <v>519</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="I34" s="12" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="J34" s="11" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="54">
       <c r="A35" s="4" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="D35" s="7" t="s">
         <v>169</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="G35" s="4" t="s">
         <v>1018</v>
       </c>
       <c r="I35" s="12" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="J35" s="11" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="54">
       <c r="A36" s="4" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="D36" s="7" t="s">
         <v>521</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="G36" s="4" t="s">
         <v>1019</v>
       </c>
       <c r="I36" s="12" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="J36" s="11" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="54">
       <c r="A37" s="4" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="D37" s="7" t="s">
         <v>166</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="G37" s="4" t="s">
         <v>1021</v>
       </c>
       <c r="I37" s="12" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="J37" s="11" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="54">
       <c r="A38" s="4" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="D38" s="7" t="s">
         <v>167</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="I38" s="12" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="J38" s="11" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="54">
       <c r="A39" s="4" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="D39" s="7" t="s">
         <v>524</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="I39" s="12" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="J39" s="11" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
     </row>
   </sheetData>
@@ -29057,16 +29784,16 @@
     </row>
     <row r="4" spans="1:18" ht="36">
       <c r="A4" s="4" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>1702</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>1703</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>517</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>556</v>
@@ -29098,13 +29825,13 @@
         <v>544</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>1722</v>
+        <v>1721</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>517</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>556</v>
@@ -29279,16 +30006,16 @@
     </row>
     <row r="10" spans="1:18" ht="36">
       <c r="A10" s="4" t="s">
+        <v>1705</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>1706</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>1707</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>164</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>889</v>
@@ -29306,10 +30033,10 @@
         <v>968</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="36">
@@ -29323,7 +30050,7 @@
         <v>164</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>889</v>
@@ -29341,10 +30068,10 @@
         <v>972</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>1709</v>
+        <v>1708</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>1709</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="36">
@@ -29486,16 +30213,16 @@
     </row>
     <row r="16" spans="1:18" ht="36">
       <c r="A16" s="4" t="s">
+        <v>1709</v>
+      </c>
+      <c r="B16" s="4" t="s">
         <v>1710</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>1711</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>164</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="E16" t="s">
         <v>942</v>
@@ -29513,10 +30240,10 @@
         <v>988</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>1712</v>
+        <v>1711</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>1712</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="36">
@@ -29530,7 +30257,7 @@
         <v>164</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="E17" t="s">
         <v>942</v>
@@ -29548,10 +30275,10 @@
         <v>990</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>1713</v>
+        <v>1712</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>1713</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="36">
@@ -29693,16 +30420,16 @@
     </row>
     <row r="22" spans="1:12">
       <c r="A22" s="4" t="s">
+        <v>1713</v>
+      </c>
+      <c r="B22" s="4" t="s">
         <v>1714</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>1715</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>164</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>1093</v>
@@ -29720,10 +30447,10 @@
         <v>1106</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>1716</v>
+        <v>1715</v>
       </c>
       <c r="L22" s="4" t="s">
-        <v>1716</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="36">
@@ -29731,13 +30458,13 @@
         <v>1085</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>1723</v>
+        <v>1722</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>164</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>1093</v>
@@ -29755,10 +30482,10 @@
         <v>1192</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
       <c r="L23" s="4" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="24" spans="1:12">
@@ -29831,152 +30558,152 @@
     </row>
     <row r="26" spans="1:12" ht="54">
       <c r="A26" s="4" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>164</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="G26" s="11" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="I26" s="11" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="54">
       <c r="A27" s="4" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>164</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="G27" s="11" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="I27" s="11" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="54">
       <c r="A28" s="4" t="s">
+        <v>1717</v>
+      </c>
+      <c r="B28" s="4" t="s">
         <v>1718</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>1719</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>164</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="F28" s="11" t="s">
+        <v>1499</v>
+      </c>
+      <c r="G28" s="11" t="s">
+        <v>1405</v>
+      </c>
+      <c r="I28" s="11" t="s">
         <v>1500</v>
       </c>
-      <c r="G28" s="11" t="s">
-        <v>1406</v>
-      </c>
-      <c r="I28" s="11" t="s">
-        <v>1501</v>
-      </c>
       <c r="K28" t="s">
-        <v>1720</v>
+        <v>1719</v>
       </c>
       <c r="L28" t="s">
-        <v>1720</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="54">
       <c r="A29" s="4" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>164</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="F29" s="11" t="s">
+        <v>1499</v>
+      </c>
+      <c r="G29" s="11" t="s">
+        <v>1405</v>
+      </c>
+      <c r="I29" s="11" t="s">
         <v>1500</v>
       </c>
-      <c r="G29" s="11" t="s">
-        <v>1406</v>
-      </c>
-      <c r="I29" s="11" t="s">
-        <v>1501</v>
-      </c>
       <c r="K29" t="s">
-        <v>1721</v>
+        <v>1720</v>
       </c>
       <c r="L29" t="s">
-        <v>1721</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="36">
       <c r="A30" s="4" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>164</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="F30" s="11" t="s">
+        <v>1501</v>
+      </c>
+      <c r="G30" s="11" t="s">
+        <v>1406</v>
+      </c>
+      <c r="I30" s="11" t="s">
         <v>1502</v>
-      </c>
-      <c r="G30" s="11" t="s">
-        <v>1407</v>
-      </c>
-      <c r="I30" s="11" t="s">
-        <v>1503</v>
       </c>
     </row>
     <row r="31" spans="1:12">
       <c r="A31" s="4" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>164</v>
@@ -29985,13 +30712,13 @@
         <v>555</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="G31" s="11" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
     </row>
   </sheetData>
@@ -30179,34 +30906,34 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="4" t="s">
+        <v>1384</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>1385</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="C6" s="4" t="s">
         <v>1386</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="D6" s="4" t="s">
         <v>1387</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="E6" s="4" t="s">
+        <v>1547</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>1388</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>1548</v>
-      </c>
-      <c r="F6" s="4" t="s">
+      <c r="H6" s="4" t="s">
         <v>1389</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="I6" s="4" t="s">
         <v>1390</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="J6" s="4" t="s">
         <v>1391</v>
       </c>
-      <c r="J6" s="4" t="s">
+      <c r="K6" s="4" t="s">
         <v>1392</v>
-      </c>
-      <c r="K6" s="4" t="s">
-        <v>1393</v>
       </c>
     </row>
   </sheetData>
@@ -30314,7 +31041,7 @@
         <v>497</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>498</v>
@@ -30944,118 +31671,118 @@
     </row>
     <row r="22" spans="1:19">
       <c r="A22" s="4" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="C22" s="4" t="s">
+        <v>1375</v>
+      </c>
+      <c r="D22" s="4" t="s">
         <v>1376</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>1377</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>188</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="O22">
         <v>100</v>
       </c>
       <c r="R22" s="4" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="S22" s="4" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="23" spans="1:19" ht="36">
       <c r="A23" s="4" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="B23" s="4" t="s">
+        <v>1374</v>
+      </c>
+      <c r="C23" s="4" t="s">
         <v>1375</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="D23" s="4" t="s">
         <v>1376</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>1377</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>188</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="O23">
         <v>130</v>
       </c>
       <c r="R23" s="11" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="S23" s="11" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="24" spans="1:19">
       <c r="A24" s="4" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="C24" s="4" t="s">
+        <v>1375</v>
+      </c>
+      <c r="D24" s="4" t="s">
         <v>1376</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>1377</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>188</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="O24">
         <v>100</v>
       </c>
       <c r="R24" s="4" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="S24" s="4" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="25" spans="1:19">
       <c r="A25" s="4" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="C25" s="4" t="s">
+        <v>1375</v>
+      </c>
+      <c r="D25" s="4" t="s">
         <v>1376</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>1377</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>188</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="O25">
         <v>300</v>
       </c>
       <c r="R25" s="4" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="S25" s="4" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
     </row>
   </sheetData>
